--- a/june 2026/STT Report JUNE 2026.xlsx
+++ b/june 2026/STT Report JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\june 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54945D6E-D8FD-4BD4-B7D6-1041B2FD55E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B87D341-F55C-414E-990D-82E9C772C9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -2596,22 +2596,22 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2623,11 +2623,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3007,44 +3007,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="107" t="s">
+      <c r="A1" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="108" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="108" t="s">
+      <c r="C1" s="103" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="108" t="s">
+      <c r="F1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="107" t="s">
+      <c r="G1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="108" t="s">
+      <c r="H1" s="103" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="107" t="s">
+      <c r="K1" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="112" t="s">
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
       <c r="S1" s="109" t="s">
         <v>10</v>
       </c>
@@ -3060,61 +3060,61 @@
       <c r="Y1" s="111"/>
       <c r="Z1" s="111"/>
       <c r="AA1" s="111"/>
-      <c r="AB1" s="105" t="s">
+      <c r="AB1" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="105" t="s">
+      <c r="AC1" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="105" t="s">
+      <c r="AD1" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="105" t="s">
+      <c r="AE1" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="105" t="s">
+      <c r="AF1" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="105" t="s">
+      <c r="AG1" s="107" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="105" t="s">
+      <c r="AI1" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="105" t="s">
+      <c r="AJ1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="105" t="s">
+      <c r="AK1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="105" t="s">
+      <c r="AL1" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="105" t="s">
+      <c r="AM1" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="103" t="s">
+      <c r="AN1" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="103" t="s">
+      <c r="AO1" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="105" t="s">
+      <c r="AP1" s="107" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="107"/>
-      <c r="B2" s="107"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="108"/>
+      <c r="A2" s="106"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="103"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -3170,23 +3170,23 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="106"/>
-      <c r="AC2" s="106"/>
-      <c r="AD2" s="106"/>
-      <c r="AE2" s="106"/>
-      <c r="AF2" s="106"/>
-      <c r="AG2" s="106"/>
+      <c r="AB2" s="108"/>
+      <c r="AC2" s="108"/>
+      <c r="AD2" s="108"/>
+      <c r="AE2" s="108"/>
+      <c r="AF2" s="108"/>
+      <c r="AG2" s="108"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="106"/>
-      <c r="AJ2" s="106"/>
-      <c r="AK2" s="106"/>
-      <c r="AL2" s="106"/>
-      <c r="AM2" s="106"/>
-      <c r="AN2" s="104"/>
-      <c r="AO2" s="104"/>
-      <c r="AP2" s="106"/>
+      <c r="AI2" s="108"/>
+      <c r="AJ2" s="108"/>
+      <c r="AK2" s="108"/>
+      <c r="AL2" s="108"/>
+      <c r="AM2" s="108"/>
+      <c r="AN2" s="113"/>
+      <c r="AO2" s="113"/>
+      <c r="AP2" s="108"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="71">
@@ -58158,13 +58158,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -58177,14 +58178,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/june 2026/STT Report JUNE 2026.xlsx
+++ b/june 2026/STT Report JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\june 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B87D341-F55C-414E-990D-82E9C772C9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC361A5C-CCE2-405F-A526-558BF3D88A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -2596,22 +2596,22 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2623,11 +2623,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3007,44 +3007,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="106" t="s">
+      <c r="A1" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="103" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="103" t="s">
+      <c r="C1" s="108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="103" t="s">
+      <c r="E1" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="103" t="s">
+      <c r="F1" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="G1" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="103" t="s">
+      <c r="H1" s="108" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="106" t="s">
+      <c r="K1" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="104" t="s">
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
       <c r="S1" s="109" t="s">
         <v>10</v>
       </c>
@@ -3060,61 +3060,61 @@
       <c r="Y1" s="111"/>
       <c r="Z1" s="111"/>
       <c r="AA1" s="111"/>
-      <c r="AB1" s="107" t="s">
+      <c r="AB1" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="107" t="s">
+      <c r="AC1" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="107" t="s">
+      <c r="AD1" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="107" t="s">
+      <c r="AE1" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="107" t="s">
+      <c r="AF1" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="107" t="s">
+      <c r="AG1" s="105" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="107" t="s">
+      <c r="AI1" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="107" t="s">
+      <c r="AJ1" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="107" t="s">
+      <c r="AK1" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="107" t="s">
+      <c r="AL1" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="107" t="s">
+      <c r="AM1" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="112" t="s">
+      <c r="AN1" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="112" t="s">
+      <c r="AO1" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="107" t="s">
+      <c r="AP1" s="105" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="103"/>
+      <c r="A2" s="107"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="108"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -3170,23 +3170,23 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="108"/>
-      <c r="AC2" s="108"/>
-      <c r="AD2" s="108"/>
-      <c r="AE2" s="108"/>
-      <c r="AF2" s="108"/>
-      <c r="AG2" s="108"/>
+      <c r="AB2" s="106"/>
+      <c r="AC2" s="106"/>
+      <c r="AD2" s="106"/>
+      <c r="AE2" s="106"/>
+      <c r="AF2" s="106"/>
+      <c r="AG2" s="106"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="108"/>
-      <c r="AJ2" s="108"/>
-      <c r="AK2" s="108"/>
-      <c r="AL2" s="108"/>
-      <c r="AM2" s="108"/>
-      <c r="AN2" s="113"/>
-      <c r="AO2" s="113"/>
-      <c r="AP2" s="108"/>
+      <c r="AI2" s="106"/>
+      <c r="AJ2" s="106"/>
+      <c r="AK2" s="106"/>
+      <c r="AL2" s="106"/>
+      <c r="AM2" s="106"/>
+      <c r="AN2" s="104"/>
+      <c r="AO2" s="104"/>
+      <c r="AP2" s="106"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="71">
@@ -58158,14 +58158,13 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -58178,13 +58177,14 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/june 2026/STT Report JUNE 2026.xlsx
+++ b/june 2026/STT Report JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\june 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC361A5C-CCE2-405F-A526-558BF3D88A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D8F349-8F74-4ACC-9B35-A54E662FEE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -2596,22 +2596,22 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2623,11 +2623,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2965,6 +2965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AP431"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3007,44 +3008,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="107" t="s">
+      <c r="A1" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="108" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="108" t="s">
+      <c r="C1" s="103" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="108" t="s">
+      <c r="F1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="107" t="s">
+      <c r="G1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="108" t="s">
+      <c r="H1" s="103" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="107" t="s">
+      <c r="K1" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="112" t="s">
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
       <c r="S1" s="109" t="s">
         <v>10</v>
       </c>
@@ -3060,61 +3061,61 @@
       <c r="Y1" s="111"/>
       <c r="Z1" s="111"/>
       <c r="AA1" s="111"/>
-      <c r="AB1" s="105" t="s">
+      <c r="AB1" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="105" t="s">
+      <c r="AC1" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="105" t="s">
+      <c r="AD1" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="105" t="s">
+      <c r="AE1" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="105" t="s">
+      <c r="AF1" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="105" t="s">
+      <c r="AG1" s="107" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="105" t="s">
+      <c r="AI1" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="105" t="s">
+      <c r="AJ1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="105" t="s">
+      <c r="AK1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="105" t="s">
+      <c r="AL1" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="105" t="s">
+      <c r="AM1" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="103" t="s">
+      <c r="AN1" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="103" t="s">
+      <c r="AO1" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="105" t="s">
+      <c r="AP1" s="107" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="107"/>
-      <c r="B2" s="107"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="108"/>
+    <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="106"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="103"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -3170,25 +3171,25 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="106"/>
-      <c r="AC2" s="106"/>
-      <c r="AD2" s="106"/>
-      <c r="AE2" s="106"/>
-      <c r="AF2" s="106"/>
-      <c r="AG2" s="106"/>
+      <c r="AB2" s="108"/>
+      <c r="AC2" s="108"/>
+      <c r="AD2" s="108"/>
+      <c r="AE2" s="108"/>
+      <c r="AF2" s="108"/>
+      <c r="AG2" s="108"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="106"/>
-      <c r="AJ2" s="106"/>
-      <c r="AK2" s="106"/>
-      <c r="AL2" s="106"/>
-      <c r="AM2" s="106"/>
-      <c r="AN2" s="104"/>
-      <c r="AO2" s="104"/>
-      <c r="AP2" s="106"/>
+      <c r="AI2" s="108"/>
+      <c r="AJ2" s="108"/>
+      <c r="AK2" s="108"/>
+      <c r="AL2" s="108"/>
+      <c r="AM2" s="108"/>
+      <c r="AN2" s="113"/>
+      <c r="AO2" s="113"/>
+      <c r="AP2" s="108"/>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="71">
         <v>46174</v>
       </c>
@@ -3325,7 +3326,7 @@
       <c r="AO3" s="6"/>
       <c r="AP3" s="12"/>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="71">
         <v>46174</v>
       </c>
@@ -3462,7 +3463,7 @@
       <c r="AO4" s="6"/>
       <c r="AP4" s="12"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="71">
         <v>46174</v>
       </c>
@@ -3599,7 +3600,7 @@
       <c r="AO5" s="6"/>
       <c r="AP5" s="12"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="71">
         <v>46174</v>
       </c>
@@ -3736,7 +3737,7 @@
       <c r="AO6" s="6"/>
       <c r="AP6" s="12"/>
     </row>
-    <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:42" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="71">
         <v>46175</v>
       </c>
@@ -3882,7 +3883,7 @@
       </c>
       <c r="AP7" s="12"/>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="71">
         <v>46175</v>
       </c>
@@ -4017,7 +4018,7 @@
       <c r="AN8"/>
       <c r="AP8" s="12"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="71">
         <v>46175</v>
       </c>
@@ -4152,7 +4153,7 @@
       <c r="AN9"/>
       <c r="AP9" s="12"/>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="71">
         <v>46175</v>
       </c>
@@ -4286,7 +4287,7 @@
       </c>
       <c r="AP10" s="12"/>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="71">
         <v>46175</v>
       </c>
@@ -4420,7 +4421,7 @@
       </c>
       <c r="AP11" s="12"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="71">
         <v>46175</v>
       </c>
@@ -4554,7 +4555,7 @@
       </c>
       <c r="AP12" s="12"/>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="71">
         <v>46176</v>
       </c>
@@ -4688,7 +4689,7 @@
       </c>
       <c r="AP13" s="12"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="71">
         <v>46176</v>
       </c>
@@ -4822,7 +4823,7 @@
       </c>
       <c r="AP14" s="12"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="71">
         <v>46176</v>
       </c>
@@ -4956,7 +4957,7 @@
       </c>
       <c r="AP15" s="12"/>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="71">
         <v>46176</v>
       </c>
@@ -5090,7 +5091,7 @@
       </c>
       <c r="AP16" s="12"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="71">
         <v>46176</v>
       </c>
@@ -5224,7 +5225,7 @@
       </c>
       <c r="AP17" s="12"/>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="71">
         <v>46176</v>
       </c>
@@ -5358,7 +5359,7 @@
       </c>
       <c r="AP18" s="12"/>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="71">
         <v>46176</v>
       </c>
@@ -5492,7 +5493,7 @@
       </c>
       <c r="AP19" s="12"/>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="71">
         <v>46176</v>
       </c>
@@ -5626,7 +5627,7 @@
       </c>
       <c r="AP20" s="12"/>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="71">
         <v>46176</v>
       </c>
@@ -5760,7 +5761,7 @@
       </c>
       <c r="AP21" s="12"/>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="71">
         <v>46176</v>
       </c>
@@ -5894,7 +5895,7 @@
       </c>
       <c r="AP22" s="12"/>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="71">
         <v>46176</v>
       </c>
@@ -6028,7 +6029,7 @@
       </c>
       <c r="AP23" s="12"/>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="71">
         <v>46177</v>
       </c>
@@ -6162,7 +6163,7 @@
       </c>
       <c r="AP24" s="12"/>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="71">
         <v>46177</v>
       </c>
@@ -6296,7 +6297,7 @@
       </c>
       <c r="AP25" s="12"/>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="71">
         <v>46177</v>
       </c>
@@ -6430,7 +6431,7 @@
       </c>
       <c r="AP26" s="12"/>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="71">
         <v>46177</v>
       </c>
@@ -6564,7 +6565,7 @@
       </c>
       <c r="AP27" s="12"/>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="71">
         <v>46177</v>
       </c>
@@ -6698,7 +6699,7 @@
       </c>
       <c r="AP28" s="12"/>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="71">
         <v>46178</v>
       </c>
@@ -6832,7 +6833,7 @@
       </c>
       <c r="AP29" s="12"/>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="71">
         <v>46178</v>
       </c>
@@ -6966,7 +6967,7 @@
       </c>
       <c r="AP30" s="12"/>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="71">
         <v>46178</v>
       </c>
@@ -7100,7 +7101,7 @@
       </c>
       <c r="AP31" s="12"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="71">
         <v>46178</v>
       </c>
@@ -7234,7 +7235,7 @@
       </c>
       <c r="AP32" s="12"/>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="71">
         <v>46178</v>
       </c>
@@ -7368,7 +7369,7 @@
       </c>
       <c r="AP33" s="12"/>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="71">
         <v>46178</v>
       </c>
@@ -7502,7 +7503,7 @@
       </c>
       <c r="AP34" s="12"/>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="71">
         <v>46209</v>
       </c>
@@ -7636,7 +7637,7 @@
       </c>
       <c r="AP35" s="12"/>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="71">
         <v>46209</v>
       </c>
@@ -7770,7 +7771,7 @@
       </c>
       <c r="AP36" s="12"/>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="71">
         <v>46209</v>
       </c>
@@ -7904,7 +7905,7 @@
       </c>
       <c r="AP37" s="12"/>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="71">
         <v>46209</v>
       </c>
@@ -8440,7 +8441,7 @@
       </c>
       <c r="AP41" s="12"/>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="71">
         <v>46211</v>
       </c>
@@ -8572,7 +8573,7 @@
       </c>
       <c r="AP42" s="12"/>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="71">
         <v>46211</v>
       </c>
@@ -8704,7 +8705,7 @@
       </c>
       <c r="AP43" s="12"/>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="71">
         <v>46211</v>
       </c>
@@ -9100,7 +9101,7 @@
       </c>
       <c r="AP46" s="12"/>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="71">
         <v>46211</v>
       </c>
@@ -9230,7 +9231,7 @@
       </c>
       <c r="AP47" s="12"/>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="71">
         <v>46211</v>
       </c>
@@ -9362,7 +9363,7 @@
       </c>
       <c r="AP48" s="12"/>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="71">
         <v>46211</v>
       </c>
@@ -9490,7 +9491,7 @@
       </c>
       <c r="AP49" s="12"/>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="71">
         <v>46211</v>
       </c>
@@ -9622,7 +9623,7 @@
       </c>
       <c r="AP50" s="12"/>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="71">
         <v>46211</v>
       </c>
@@ -9752,7 +9753,7 @@
       </c>
       <c r="AP51" s="12"/>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="71">
         <v>46212</v>
       </c>
@@ -9886,7 +9887,7 @@
       </c>
       <c r="AP52" s="12"/>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="71">
         <v>46212</v>
       </c>
@@ -10016,7 +10017,7 @@
       </c>
       <c r="AP53" s="12"/>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="71">
         <v>46212</v>
       </c>
@@ -10150,7 +10151,7 @@
       </c>
       <c r="AP54" s="12"/>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="71">
         <v>46212</v>
       </c>
@@ -10284,7 +10285,7 @@
       </c>
       <c r="AP55" s="12"/>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="71">
         <v>46212</v>
       </c>
@@ -10418,7 +10419,7 @@
       </c>
       <c r="AP56" s="12"/>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="71">
         <v>46212</v>
       </c>
@@ -10552,7 +10553,7 @@
       </c>
       <c r="AP57" s="12"/>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="71">
         <v>46212</v>
       </c>
@@ -10686,7 +10687,7 @@
       </c>
       <c r="AP58" s="12"/>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="71">
         <v>46212</v>
       </c>
@@ -10820,7 +10821,7 @@
       </c>
       <c r="AP59" s="12"/>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="71">
         <v>46212</v>
       </c>
@@ -11218,7 +11219,7 @@
       </c>
       <c r="AP62" s="12"/>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="71">
         <v>46212</v>
       </c>
@@ -11352,7 +11353,7 @@
       </c>
       <c r="AP63" s="12"/>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="71">
         <v>46212</v>
       </c>
@@ -11486,7 +11487,7 @@
       </c>
       <c r="AP64" s="12"/>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="71">
         <v>46212</v>
       </c>
@@ -11620,7 +11621,7 @@
       </c>
       <c r="AP65" s="12"/>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="71">
         <v>46212</v>
       </c>
@@ -11754,7 +11755,7 @@
       </c>
       <c r="AP66" s="12"/>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="71">
         <v>46212</v>
       </c>
@@ -11888,7 +11889,7 @@
       </c>
       <c r="AP67" s="12"/>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="71">
         <v>46212</v>
       </c>
@@ -12022,7 +12023,7 @@
       </c>
       <c r="AP68" s="12"/>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="71">
         <v>46212</v>
       </c>
@@ -12156,7 +12157,7 @@
       </c>
       <c r="AP69" s="12"/>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="71">
         <v>46212</v>
       </c>
@@ -12290,7 +12291,7 @@
       </c>
       <c r="AP70" s="12"/>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="71">
         <v>46212</v>
       </c>
@@ -12424,7 +12425,7 @@
       </c>
       <c r="AP71" s="12"/>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="71">
         <v>46183</v>
       </c>
@@ -12558,7 +12559,7 @@
       </c>
       <c r="AP72" s="12"/>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="71">
         <v>46183</v>
       </c>
@@ -12692,7 +12693,7 @@
       </c>
       <c r="AP73" s="12"/>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="71">
         <v>46183</v>
       </c>
@@ -12826,7 +12827,7 @@
       </c>
       <c r="AP74" s="12"/>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="71">
         <v>46183</v>
       </c>
@@ -12960,7 +12961,7 @@
       </c>
       <c r="AP75" s="12"/>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="71">
         <v>46183</v>
       </c>
@@ -13490,7 +13491,7 @@
       </c>
       <c r="AP79" s="12"/>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="71">
         <v>46184</v>
       </c>
@@ -13624,7 +13625,7 @@
       </c>
       <c r="AP80" s="12"/>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="71">
         <v>46184</v>
       </c>
@@ -13758,7 +13759,7 @@
       </c>
       <c r="AP81" s="12"/>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="71">
         <v>46184</v>
       </c>
@@ -13892,7 +13893,7 @@
       </c>
       <c r="AP82" s="12"/>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="71">
         <v>46184</v>
       </c>
@@ -14026,7 +14027,7 @@
       </c>
       <c r="AP83" s="12"/>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="71">
         <v>46184</v>
       </c>
@@ -14160,7 +14161,7 @@
       </c>
       <c r="AP84" s="12"/>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="71">
         <v>46184</v>
       </c>
@@ -14294,7 +14295,7 @@
       </c>
       <c r="AP85" s="12"/>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="71">
         <v>46184</v>
       </c>
@@ -14428,7 +14429,7 @@
       </c>
       <c r="AP86" s="12"/>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="71">
         <v>46184</v>
       </c>
@@ -14562,7 +14563,7 @@
       </c>
       <c r="AP87" s="12"/>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="71">
         <v>46184</v>
       </c>
@@ -14696,7 +14697,7 @@
       </c>
       <c r="AP88" s="12"/>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="71">
         <v>46184</v>
       </c>
@@ -14830,7 +14831,7 @@
       </c>
       <c r="AP89" s="12"/>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="71">
         <v>46184</v>
       </c>
@@ -14964,7 +14965,7 @@
       </c>
       <c r="AP90" s="12"/>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="71">
         <v>46184</v>
       </c>
@@ -15624,7 +15625,7 @@
       </c>
       <c r="AP95" s="12"/>
     </row>
-    <row r="96" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="71">
         <v>46185</v>
       </c>
@@ -15758,7 +15759,7 @@
       </c>
       <c r="AP96" s="12"/>
     </row>
-    <row r="97" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="71">
         <v>46185</v>
       </c>
@@ -15892,7 +15893,7 @@
       </c>
       <c r="AP97" s="12"/>
     </row>
-    <row r="98" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="71">
         <v>46185</v>
       </c>
@@ -16026,7 +16027,7 @@
       </c>
       <c r="AP98" s="12"/>
     </row>
-    <row r="99" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="71">
         <v>46185</v>
       </c>
@@ -16160,7 +16161,7 @@
       </c>
       <c r="AP99" s="12"/>
     </row>
-    <row r="100" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="71">
         <v>46185</v>
       </c>
@@ -16294,7 +16295,7 @@
       </c>
       <c r="AP100" s="12"/>
     </row>
-    <row r="101" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="71">
         <v>46185</v>
       </c>
@@ -16428,7 +16429,7 @@
       </c>
       <c r="AP101" s="12"/>
     </row>
-    <row r="102" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="71">
         <v>46185</v>
       </c>
@@ -16562,7 +16563,7 @@
       </c>
       <c r="AP102" s="12"/>
     </row>
-    <row r="103" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="71">
         <v>46185</v>
       </c>
@@ -16696,7 +16697,7 @@
       </c>
       <c r="AP103" s="12"/>
     </row>
-    <row r="104" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="71">
         <v>46185</v>
       </c>
@@ -16830,7 +16831,7 @@
       </c>
       <c r="AP104" s="12"/>
     </row>
-    <row r="105" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="71">
         <v>46185</v>
       </c>
@@ -16964,7 +16965,7 @@
       </c>
       <c r="AP105" s="12"/>
     </row>
-    <row r="106" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="71">
         <v>46185</v>
       </c>
@@ -17096,7 +17097,7 @@
       </c>
       <c r="AP106" s="12"/>
     </row>
-    <row r="107" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="71">
         <v>46186</v>
       </c>
@@ -17230,7 +17231,7 @@
       </c>
       <c r="AP107" s="12"/>
     </row>
-    <row r="108" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="71">
         <v>46186</v>
       </c>
@@ -17364,7 +17365,7 @@
       </c>
       <c r="AP108" s="12"/>
     </row>
-    <row r="109" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="71">
         <v>46186</v>
       </c>
@@ -17498,7 +17499,7 @@
       </c>
       <c r="AP109" s="12"/>
     </row>
-    <row r="110" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="71">
         <v>46186</v>
       </c>
@@ -17632,7 +17633,7 @@
       </c>
       <c r="AP110" s="12"/>
     </row>
-    <row r="111" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="71">
         <v>46186</v>
       </c>
@@ -17766,7 +17767,7 @@
       </c>
       <c r="AP111" s="12"/>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="71">
         <v>46186</v>
       </c>
@@ -17900,7 +17901,7 @@
       </c>
       <c r="AP112" s="12"/>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="71">
         <v>46186</v>
       </c>
@@ -18034,7 +18035,7 @@
       </c>
       <c r="AP113" s="12"/>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="71">
         <v>46186</v>
       </c>
@@ -18168,7 +18169,7 @@
       </c>
       <c r="AP114" s="12"/>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="71">
         <v>46186</v>
       </c>
@@ -18302,7 +18303,7 @@
       </c>
       <c r="AP115" s="12"/>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="71">
         <v>46186</v>
       </c>
@@ -18436,7 +18437,7 @@
       </c>
       <c r="AP116" s="12"/>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="71">
         <v>46186</v>
       </c>
@@ -18570,7 +18571,7 @@
       </c>
       <c r="AP117" s="12"/>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="71">
         <v>46186</v>
       </c>
@@ -18704,7 +18705,7 @@
       </c>
       <c r="AP118" s="12"/>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="71">
         <v>46186</v>
       </c>
@@ -18838,7 +18839,7 @@
       </c>
       <c r="AP119" s="12"/>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="71">
         <v>46186</v>
       </c>
@@ -18972,7 +18973,7 @@
       </c>
       <c r="AP120" s="12"/>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="71">
         <v>46188</v>
       </c>
@@ -19106,7 +19107,7 @@
       </c>
       <c r="AP121" s="12"/>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="71">
         <v>46188</v>
       </c>
@@ -19240,7 +19241,7 @@
       </c>
       <c r="AP122" s="12"/>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="71">
         <v>46188</v>
       </c>
@@ -19374,7 +19375,7 @@
       </c>
       <c r="AP123" s="12"/>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="71">
         <v>46188</v>
       </c>
@@ -19508,7 +19509,7 @@
       </c>
       <c r="AP124" s="12"/>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="71">
         <v>46188</v>
       </c>
@@ -19642,7 +19643,7 @@
       </c>
       <c r="AP125" s="12"/>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="71">
         <v>46188</v>
       </c>
@@ -19776,7 +19777,7 @@
       </c>
       <c r="AP126" s="12"/>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="71">
         <v>46188</v>
       </c>
@@ -19910,7 +19911,7 @@
       </c>
       <c r="AP127" s="12"/>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="71">
         <v>46188</v>
       </c>
@@ -20044,7 +20045,7 @@
       </c>
       <c r="AP128" s="12"/>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="71">
         <v>46188</v>
       </c>
@@ -20178,7 +20179,7 @@
       </c>
       <c r="AP129" s="12"/>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="71">
         <v>46188</v>
       </c>
@@ -20310,7 +20311,7 @@
       </c>
       <c r="AP130" s="12"/>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="71">
         <v>46188</v>
       </c>
@@ -20444,7 +20445,7 @@
       </c>
       <c r="AP131" s="12"/>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="71">
         <v>46189</v>
       </c>
@@ -20576,7 +20577,7 @@
       </c>
       <c r="AP132" s="12"/>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="71">
         <v>46189</v>
       </c>
@@ -20708,7 +20709,7 @@
       </c>
       <c r="AP133" s="12"/>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="71">
         <v>46189</v>
       </c>
@@ -20840,7 +20841,7 @@
       </c>
       <c r="AP134" s="12"/>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="71">
         <v>46189</v>
       </c>
@@ -21240,7 +21241,7 @@
       </c>
       <c r="AP137" s="12"/>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="71">
         <v>46189</v>
       </c>
@@ -21374,7 +21375,7 @@
       </c>
       <c r="AP138" s="12"/>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="71">
         <v>46189</v>
       </c>
@@ -21508,7 +21509,7 @@
       </c>
       <c r="AP139" s="12"/>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="71">
         <v>46189</v>
       </c>
@@ -21642,7 +21643,7 @@
       </c>
       <c r="AP140" s="12"/>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="71">
         <v>46189</v>
       </c>
@@ -21776,7 +21777,7 @@
       </c>
       <c r="AP141" s="12"/>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="71">
         <v>46189</v>
       </c>
@@ -21910,7 +21911,7 @@
       </c>
       <c r="AP142" s="12"/>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="71">
         <v>46189</v>
       </c>
@@ -22044,7 +22045,7 @@
       </c>
       <c r="AP143" s="12"/>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="71">
         <v>46189</v>
       </c>
@@ -22178,7 +22179,7 @@
       </c>
       <c r="AP144" s="12"/>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="71">
         <v>46189</v>
       </c>
@@ -22312,7 +22313,7 @@
       </c>
       <c r="AP145" s="12"/>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="71">
         <v>46189</v>
       </c>
@@ -22446,7 +22447,7 @@
       </c>
       <c r="AP146" s="12"/>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="71">
         <v>46189</v>
       </c>
@@ -22580,7 +22581,7 @@
       </c>
       <c r="AP147" s="12"/>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="71">
         <v>46189</v>
       </c>
@@ -22714,7 +22715,7 @@
       </c>
       <c r="AP148" s="12"/>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="71">
         <v>46189</v>
       </c>
@@ -22848,7 +22849,7 @@
       </c>
       <c r="AP149" s="12"/>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="71">
         <v>46189</v>
       </c>
@@ -22982,7 +22983,7 @@
       </c>
       <c r="AP150" s="12"/>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="71">
         <v>46189</v>
       </c>
@@ -23116,7 +23117,7 @@
       </c>
       <c r="AP151" s="12"/>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="71">
         <v>46190</v>
       </c>
@@ -23250,7 +23251,7 @@
       </c>
       <c r="AP152" s="12"/>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="71">
         <v>46190</v>
       </c>
@@ -23384,7 +23385,7 @@
       </c>
       <c r="AP153" s="12"/>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="71">
         <v>46190</v>
       </c>
@@ -23516,7 +23517,7 @@
       </c>
       <c r="AP154" s="12"/>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="71">
         <v>46190</v>
       </c>
@@ -23648,7 +23649,7 @@
       </c>
       <c r="AP155" s="12"/>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="71">
         <v>46190</v>
       </c>
@@ -23780,7 +23781,7 @@
       </c>
       <c r="AP156" s="12"/>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="71">
         <v>46190</v>
       </c>
@@ -23914,7 +23915,7 @@
       </c>
       <c r="AP157" s="12"/>
     </row>
-    <row r="158" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="71">
         <v>46190</v>
       </c>
@@ -24048,7 +24049,7 @@
       </c>
       <c r="AP158" s="12"/>
     </row>
-    <row r="159" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="71">
         <v>46190</v>
       </c>
@@ -24182,7 +24183,7 @@
       </c>
       <c r="AP159" s="12"/>
     </row>
-    <row r="160" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="71">
         <v>46190</v>
       </c>
@@ -24844,7 +24845,7 @@
       </c>
       <c r="AP164" s="12"/>
     </row>
-    <row r="165" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="71">
         <v>46190</v>
       </c>
@@ -24976,7 +24977,7 @@
       </c>
       <c r="AP165" s="12"/>
     </row>
-    <row r="166" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="71">
         <v>46190</v>
       </c>
@@ -25108,7 +25109,7 @@
       </c>
       <c r="AP166" s="12"/>
     </row>
-    <row r="167" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="71">
         <v>46190</v>
       </c>
@@ -25240,7 +25241,7 @@
       </c>
       <c r="AP167" s="12"/>
     </row>
-    <row r="168" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="71">
         <v>46190</v>
       </c>
@@ -25372,7 +25373,7 @@
       </c>
       <c r="AP168" s="12"/>
     </row>
-    <row r="169" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="71">
         <v>46190</v>
       </c>
@@ -25504,7 +25505,7 @@
       </c>
       <c r="AP169" s="12"/>
     </row>
-    <row r="170" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="71">
         <v>46190</v>
       </c>
@@ -25636,7 +25637,7 @@
       </c>
       <c r="AP170" s="12"/>
     </row>
-    <row r="171" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="71">
         <v>46190</v>
       </c>
@@ -25768,7 +25769,7 @@
       </c>
       <c r="AP171" s="12"/>
     </row>
-    <row r="172" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="71">
         <v>46190</v>
       </c>
@@ -25900,7 +25901,7 @@
       </c>
       <c r="AP172" s="12"/>
     </row>
-    <row r="173" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="71">
         <v>46190</v>
       </c>
@@ -26032,7 +26033,7 @@
       </c>
       <c r="AP173" s="12"/>
     </row>
-    <row r="174" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="71">
         <v>46190</v>
       </c>
@@ -26164,7 +26165,7 @@
       </c>
       <c r="AP174" s="12"/>
     </row>
-    <row r="175" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="71">
         <v>46190</v>
       </c>
@@ -26296,7 +26297,7 @@
       </c>
       <c r="AP175" s="12"/>
     </row>
-    <row r="176" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="71">
         <v>46190</v>
       </c>
@@ -26428,7 +26429,7 @@
       </c>
       <c r="AP176" s="12"/>
     </row>
-    <row r="177" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="71">
         <v>46191</v>
       </c>
@@ -26562,7 +26563,7 @@
       </c>
       <c r="AP177" s="12"/>
     </row>
-    <row r="178" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="71">
         <v>46191</v>
       </c>
@@ -26696,7 +26697,7 @@
       </c>
       <c r="AP178" s="12"/>
     </row>
-    <row r="179" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="71">
         <v>46191</v>
       </c>
@@ -26830,7 +26831,7 @@
       </c>
       <c r="AP179" s="12"/>
     </row>
-    <row r="180" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="71">
         <v>46191</v>
       </c>
@@ -26964,7 +26965,7 @@
       </c>
       <c r="AP180" s="12"/>
     </row>
-    <row r="181" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="71">
         <v>46191</v>
       </c>
@@ -27098,7 +27099,7 @@
       </c>
       <c r="AP181" s="12"/>
     </row>
-    <row r="182" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="71">
         <v>46191</v>
       </c>
@@ -27232,7 +27233,7 @@
       </c>
       <c r="AP182" s="12"/>
     </row>
-    <row r="183" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="71">
         <v>46191</v>
       </c>
@@ -27366,7 +27367,7 @@
       </c>
       <c r="AP183" s="12"/>
     </row>
-    <row r="184" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="71">
         <v>46191</v>
       </c>
@@ -27500,7 +27501,7 @@
       </c>
       <c r="AP184" s="12"/>
     </row>
-    <row r="185" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="71">
         <v>46191</v>
       </c>
@@ -27634,7 +27635,7 @@
       </c>
       <c r="AP185" s="12"/>
     </row>
-    <row r="186" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="71">
         <v>46191</v>
       </c>
@@ -28428,7 +28429,7 @@
       </c>
       <c r="AP191" s="12"/>
     </row>
-    <row r="192" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="71">
         <v>46191</v>
       </c>
@@ -28560,7 +28561,7 @@
       </c>
       <c r="AP192" s="12"/>
     </row>
-    <row r="193" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="71">
         <v>46191</v>
       </c>
@@ -28692,7 +28693,7 @@
       </c>
       <c r="AP193" s="12"/>
     </row>
-    <row r="194" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="71">
         <v>46191</v>
       </c>
@@ -28824,7 +28825,7 @@
       </c>
       <c r="AP194" s="12"/>
     </row>
-    <row r="195" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="71">
         <v>46191</v>
       </c>
@@ -28956,7 +28957,7 @@
       </c>
       <c r="AP195" s="12"/>
     </row>
-    <row r="196" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="71">
         <v>46191</v>
       </c>
@@ -29088,7 +29089,7 @@
       </c>
       <c r="AP196" s="12"/>
     </row>
-    <row r="197" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="71">
         <v>46191</v>
       </c>
@@ -29220,7 +29221,7 @@
       </c>
       <c r="AP197" s="12"/>
     </row>
-    <row r="198" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="71">
         <v>46191</v>
       </c>
@@ -29352,7 +29353,7 @@
       </c>
       <c r="AP198" s="12"/>
     </row>
-    <row r="199" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="71">
         <v>46191</v>
       </c>
@@ -29484,7 +29485,7 @@
       </c>
       <c r="AP199" s="12"/>
     </row>
-    <row r="200" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="71">
         <v>46191</v>
       </c>
@@ -29616,7 +29617,7 @@
       </c>
       <c r="AP200" s="12"/>
     </row>
-    <row r="201" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="71">
         <v>46191</v>
       </c>
@@ -29748,7 +29749,7 @@
       </c>
       <c r="AP201" s="12"/>
     </row>
-    <row r="202" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="71">
         <v>46191</v>
       </c>
@@ -29880,7 +29881,7 @@
       </c>
       <c r="AP202" s="12"/>
     </row>
-    <row r="203" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="71">
         <v>46191</v>
       </c>
@@ -30012,7 +30013,7 @@
       </c>
       <c r="AP203" s="12"/>
     </row>
-    <row r="204" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="71">
         <v>46191</v>
       </c>
@@ -30144,7 +30145,7 @@
       </c>
       <c r="AP204" s="12"/>
     </row>
-    <row r="205" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="71">
         <v>46191</v>
       </c>
@@ -30408,7 +30409,7 @@
       </c>
       <c r="AP206" s="12"/>
     </row>
-    <row r="207" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="71">
         <v>46192</v>
       </c>
@@ -30540,7 +30541,7 @@
       </c>
       <c r="AP207" s="12"/>
     </row>
-    <row r="208" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="71">
         <v>46192</v>
       </c>
@@ -30672,7 +30673,7 @@
       </c>
       <c r="AP208" s="12"/>
     </row>
-    <row r="209" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="71">
         <v>46192</v>
       </c>
@@ -30806,7 +30807,7 @@
       </c>
       <c r="AP209" s="12"/>
     </row>
-    <row r="210" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="71">
         <v>46192</v>
       </c>
@@ -30938,7 +30939,7 @@
       </c>
       <c r="AP210" s="12"/>
     </row>
-    <row r="211" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="71">
         <v>46192</v>
       </c>
@@ -31070,7 +31071,7 @@
       </c>
       <c r="AP211" s="12"/>
     </row>
-    <row r="212" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="71">
         <v>46192</v>
       </c>
@@ -31202,7 +31203,7 @@
       </c>
       <c r="AP212" s="12"/>
     </row>
-    <row r="213" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="71">
         <v>46192</v>
       </c>
@@ -31334,7 +31335,7 @@
       </c>
       <c r="AP213" s="12"/>
     </row>
-    <row r="214" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="71">
         <v>46192</v>
       </c>
@@ -31466,7 +31467,7 @@
       </c>
       <c r="AP214" s="12"/>
     </row>
-    <row r="215" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="71">
         <v>46192</v>
       </c>
@@ -31598,7 +31599,7 @@
       </c>
       <c r="AP215" s="12"/>
     </row>
-    <row r="216" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="71">
         <v>46192</v>
       </c>
@@ -31730,7 +31731,7 @@
       </c>
       <c r="AP216" s="12"/>
     </row>
-    <row r="217" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="71">
         <v>46192</v>
       </c>
@@ -31862,7 +31863,7 @@
       </c>
       <c r="AP217" s="12"/>
     </row>
-    <row r="218" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="71">
         <v>46192</v>
       </c>
@@ -31994,7 +31995,7 @@
       </c>
       <c r="AP218" s="12"/>
     </row>
-    <row r="219" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="71">
         <v>46192</v>
       </c>
@@ -32126,7 +32127,7 @@
       </c>
       <c r="AP219" s="12"/>
     </row>
-    <row r="220" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="71">
         <v>46192</v>
       </c>
@@ -32258,7 +32259,7 @@
       </c>
       <c r="AP220" s="12"/>
     </row>
-    <row r="221" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="71">
         <v>46192</v>
       </c>
@@ -32390,7 +32391,7 @@
       </c>
       <c r="AP221" s="12"/>
     </row>
-    <row r="222" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="71">
         <v>46192</v>
       </c>
@@ -32522,7 +32523,7 @@
       </c>
       <c r="AP222" s="12"/>
     </row>
-    <row r="223" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="71">
         <v>46192</v>
       </c>
@@ -32654,7 +32655,7 @@
       </c>
       <c r="AP223" s="12"/>
     </row>
-    <row r="224" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="71">
         <v>46192</v>
       </c>
@@ -32786,7 +32787,7 @@
       </c>
       <c r="AP224" s="12"/>
     </row>
-    <row r="225" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="71">
         <v>46192</v>
       </c>
@@ -32918,7 +32919,7 @@
       </c>
       <c r="AP225" s="12"/>
     </row>
-    <row r="226" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="71">
         <v>46192</v>
       </c>
@@ -33314,7 +33315,7 @@
       </c>
       <c r="AP228" s="12"/>
     </row>
-    <row r="229" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="71">
         <v>46193</v>
       </c>
@@ -33448,7 +33449,7 @@
       </c>
       <c r="AP229" s="12"/>
     </row>
-    <row r="230" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="71">
         <v>46193</v>
       </c>
@@ -33582,7 +33583,7 @@
       </c>
       <c r="AP230" s="12"/>
     </row>
-    <row r="231" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="71">
         <v>46193</v>
       </c>
@@ -33716,7 +33717,7 @@
       </c>
       <c r="AP231" s="12"/>
     </row>
-    <row r="232" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="71">
         <v>46193</v>
       </c>
@@ -33850,7 +33851,7 @@
       </c>
       <c r="AP232" s="12"/>
     </row>
-    <row r="233" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="71">
         <v>46193</v>
       </c>
@@ -33984,7 +33985,7 @@
       </c>
       <c r="AP233" s="12"/>
     </row>
-    <row r="234" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="71">
         <v>46193</v>
       </c>
@@ -34118,7 +34119,7 @@
       </c>
       <c r="AP234" s="12"/>
     </row>
-    <row r="235" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="71">
         <v>46193</v>
       </c>
@@ -34252,7 +34253,7 @@
       </c>
       <c r="AP235" s="12"/>
     </row>
-    <row r="236" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="71">
         <v>46193</v>
       </c>
@@ -34386,7 +34387,7 @@
       </c>
       <c r="AP236" s="12"/>
     </row>
-    <row r="237" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="71">
         <v>46193</v>
       </c>
@@ -34520,7 +34521,7 @@
       </c>
       <c r="AP237" s="12"/>
     </row>
-    <row r="238" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="71">
         <v>46193</v>
       </c>
@@ -34654,7 +34655,7 @@
       </c>
       <c r="AP238" s="12"/>
     </row>
-    <row r="239" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="71">
         <v>46193</v>
       </c>
@@ -34788,7 +34789,7 @@
       </c>
       <c r="AP239" s="12"/>
     </row>
-    <row r="240" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="71">
         <v>46193</v>
       </c>
@@ -34922,7 +34923,7 @@
       </c>
       <c r="AP240" s="12"/>
     </row>
-    <row r="241" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="71">
         <v>46193</v>
       </c>
@@ -35056,7 +35057,7 @@
       </c>
       <c r="AP241" s="12"/>
     </row>
-    <row r="242" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="71">
         <v>46193</v>
       </c>
@@ -35190,7 +35191,7 @@
       </c>
       <c r="AP242" s="12"/>
     </row>
-    <row r="243" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="71">
         <v>46193</v>
       </c>
@@ -35324,7 +35325,7 @@
       </c>
       <c r="AP243" s="12"/>
     </row>
-    <row r="244" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="71">
         <v>46193</v>
       </c>
@@ -35458,7 +35459,7 @@
       </c>
       <c r="AP244" s="12"/>
     </row>
-    <row r="245" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="71">
         <v>46193</v>
       </c>
@@ -35592,7 +35593,7 @@
       </c>
       <c r="AP245" s="12"/>
     </row>
-    <row r="246" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="71">
         <v>46193</v>
       </c>
@@ -35726,7 +35727,7 @@
       </c>
       <c r="AP246" s="12"/>
     </row>
-    <row r="247" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="71">
         <v>46193</v>
       </c>
@@ -35860,7 +35861,7 @@
       </c>
       <c r="AP247" s="12"/>
     </row>
-    <row r="248" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="71">
         <v>46193</v>
       </c>
@@ -35994,7 +35995,7 @@
       </c>
       <c r="AP248" s="12"/>
     </row>
-    <row r="249" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="71">
         <v>46193</v>
       </c>
@@ -36390,7 +36391,7 @@
       </c>
       <c r="AP251" s="12"/>
     </row>
-    <row r="252" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="71">
         <v>46195</v>
       </c>
@@ -36518,7 +36519,7 @@
       </c>
       <c r="AP252" s="12"/>
     </row>
-    <row r="253" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="71">
         <v>46195</v>
       </c>
@@ -36776,7 +36777,7 @@
       </c>
       <c r="AP254" s="12"/>
     </row>
-    <row r="255" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="71">
         <v>46195</v>
       </c>
@@ -36900,7 +36901,7 @@
       </c>
       <c r="AP255" s="12"/>
     </row>
-    <row r="256" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="71">
         <v>46195</v>
       </c>
@@ -37032,7 +37033,7 @@
       </c>
       <c r="AP256" s="12"/>
     </row>
-    <row r="257" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="71">
         <v>46195</v>
       </c>
@@ -37158,7 +37159,7 @@
       </c>
       <c r="AP257" s="12"/>
     </row>
-    <row r="258" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="71">
         <v>46195</v>
       </c>
@@ -37284,7 +37285,7 @@
       </c>
       <c r="AP258" s="12"/>
     </row>
-    <row r="259" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="71">
         <v>46195</v>
       </c>
@@ -37416,7 +37417,7 @@
       </c>
       <c r="AP259" s="12"/>
     </row>
-    <row r="260" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="71">
         <v>46195</v>
       </c>
@@ -37540,7 +37541,7 @@
       </c>
       <c r="AP260" s="12"/>
     </row>
-    <row r="261" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="71">
         <v>46195</v>
       </c>
@@ -37662,7 +37663,7 @@
       </c>
       <c r="AP261" s="12"/>
     </row>
-    <row r="262" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="71">
         <v>46195</v>
       </c>
@@ -37788,7 +37789,7 @@
       </c>
       <c r="AP262" s="12"/>
     </row>
-    <row r="263" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="71">
         <v>46195</v>
       </c>
@@ -37916,7 +37917,7 @@
       </c>
       <c r="AP263" s="12"/>
     </row>
-    <row r="264" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="71">
         <v>46195</v>
       </c>
@@ -38044,7 +38045,7 @@
       </c>
       <c r="AP264" s="12"/>
     </row>
-    <row r="265" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="71">
         <v>46195</v>
       </c>
@@ -38170,7 +38171,7 @@
       </c>
       <c r="AP265" s="12"/>
     </row>
-    <row r="266" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="71">
         <v>46195</v>
       </c>
@@ -38292,7 +38293,7 @@
       </c>
       <c r="AP266" s="12"/>
     </row>
-    <row r="267" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="71">
         <v>46195</v>
       </c>
@@ -38424,7 +38425,7 @@
       </c>
       <c r="AP267" s="12"/>
     </row>
-    <row r="268" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="71">
         <v>46195</v>
       </c>
@@ -38550,7 +38551,7 @@
       </c>
       <c r="AP268" s="12"/>
     </row>
-    <row r="269" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="71">
         <v>46195</v>
       </c>
@@ -38678,7 +38679,7 @@
       </c>
       <c r="AP269" s="12"/>
     </row>
-    <row r="270" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="71">
         <v>46195</v>
       </c>
@@ -38804,7 +38805,7 @@
       </c>
       <c r="AP270" s="12"/>
     </row>
-    <row r="271" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="71">
         <v>46195</v>
       </c>
@@ -38936,7 +38937,7 @@
       </c>
       <c r="AP271" s="12"/>
     </row>
-    <row r="272" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="71">
         <v>46195</v>
       </c>
@@ -39064,7 +39065,7 @@
       </c>
       <c r="AP272" s="12"/>
     </row>
-    <row r="273" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="71">
         <v>46195</v>
       </c>
@@ -39190,7 +39191,7 @@
       </c>
       <c r="AP273" s="12"/>
     </row>
-    <row r="274" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="71">
         <v>46195</v>
       </c>
@@ -39314,7 +39315,7 @@
       </c>
       <c r="AP274" s="12"/>
     </row>
-    <row r="275" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="71">
         <v>46195</v>
       </c>
@@ -39438,7 +39439,7 @@
       </c>
       <c r="AP275" s="12"/>
     </row>
-    <row r="276" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="71">
         <v>46195</v>
       </c>
@@ -39564,7 +39565,7 @@
       </c>
       <c r="AP276" s="12"/>
     </row>
-    <row r="277" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="71">
         <v>46195</v>
       </c>
@@ -39686,7 +39687,7 @@
       </c>
       <c r="AP277" s="12"/>
     </row>
-    <row r="278" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="71">
         <v>46195</v>
       </c>
@@ -39808,7 +39809,7 @@
       </c>
       <c r="AP278" s="12"/>
     </row>
-    <row r="279" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="71">
         <v>46195</v>
       </c>
@@ -39930,7 +39931,7 @@
       </c>
       <c r="AP279" s="12"/>
     </row>
-    <row r="280" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="71">
         <v>46195</v>
       </c>
@@ -40064,7 +40065,7 @@
       </c>
       <c r="AP280" s="12"/>
     </row>
-    <row r="281" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="71">
         <v>46196</v>
       </c>
@@ -40186,7 +40187,7 @@
       </c>
       <c r="AP281" s="12"/>
     </row>
-    <row r="282" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="71">
         <v>46196</v>
       </c>
@@ -40312,7 +40313,7 @@
       </c>
       <c r="AP282" s="12"/>
     </row>
-    <row r="283" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="71">
         <v>46196</v>
       </c>
@@ -40444,7 +40445,7 @@
       </c>
       <c r="AP283" s="12"/>
     </row>
-    <row r="284" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="71">
         <v>46196</v>
       </c>
@@ -40572,7 +40573,7 @@
       </c>
       <c r="AP284" s="12"/>
     </row>
-    <row r="285" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="71">
         <v>46196</v>
       </c>
@@ -40700,7 +40701,7 @@
       </c>
       <c r="AP285" s="12"/>
     </row>
-    <row r="286" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="71">
         <v>46196</v>
       </c>
@@ -40828,7 +40829,7 @@
       </c>
       <c r="AP286" s="12"/>
     </row>
-    <row r="287" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="71">
         <v>46196</v>
       </c>
@@ -40962,7 +40963,7 @@
       </c>
       <c r="AP287" s="12"/>
     </row>
-    <row r="288" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="71">
         <v>46196</v>
       </c>
@@ -41086,7 +41087,7 @@
       </c>
       <c r="AP288" s="12"/>
     </row>
-    <row r="289" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="71">
         <v>46196</v>
       </c>
@@ -41208,7 +41209,7 @@
       </c>
       <c r="AP289" s="12"/>
     </row>
-    <row r="290" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="71">
         <v>46196</v>
       </c>
@@ -41330,7 +41331,7 @@
       </c>
       <c r="AP290" s="12"/>
     </row>
-    <row r="291" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="71">
         <v>46196</v>
       </c>
@@ -41452,7 +41453,7 @@
       </c>
       <c r="AP291" s="12"/>
     </row>
-    <row r="292" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="71">
         <v>46196</v>
       </c>
@@ -41580,7 +41581,7 @@
       </c>
       <c r="AP292" s="12"/>
     </row>
-    <row r="293" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="71">
         <v>46196</v>
       </c>
@@ -41706,7 +41707,7 @@
       </c>
       <c r="AP293" s="12"/>
     </row>
-    <row r="294" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="71">
         <v>46196</v>
       </c>
@@ -41838,7 +41839,7 @@
       </c>
       <c r="AP294" s="12"/>
     </row>
-    <row r="295" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="71">
         <v>46196</v>
       </c>
@@ -41970,7 +41971,7 @@
       </c>
       <c r="AP295" s="12"/>
     </row>
-    <row r="296" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="71">
         <v>46196</v>
       </c>
@@ -42096,7 +42097,7 @@
       </c>
       <c r="AP296" s="12"/>
     </row>
-    <row r="297" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="71">
         <v>46196</v>
       </c>
@@ -42228,7 +42229,7 @@
       </c>
       <c r="AP297" s="12"/>
     </row>
-    <row r="298" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="71">
         <v>46196</v>
       </c>
@@ -42350,7 +42351,7 @@
       </c>
       <c r="AP298" s="12"/>
     </row>
-    <row r="299" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="71">
         <v>46196</v>
       </c>
@@ -42472,7 +42473,7 @@
       </c>
       <c r="AP299" s="12"/>
     </row>
-    <row r="300" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="71">
         <v>46197</v>
       </c>
@@ -42596,7 +42597,7 @@
       </c>
       <c r="AP300" s="12"/>
     </row>
-    <row r="301" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="71">
         <v>46197</v>
       </c>
@@ -42724,7 +42725,7 @@
       </c>
       <c r="AP301" s="12"/>
     </row>
-    <row r="302" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="71">
         <v>46197</v>
       </c>
@@ -42852,7 +42853,7 @@
       </c>
       <c r="AP302" s="12"/>
     </row>
-    <row r="303" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="71">
         <v>46197</v>
       </c>
@@ -42978,7 +42979,7 @@
       </c>
       <c r="AP303" s="12"/>
     </row>
-    <row r="304" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="71">
         <v>46197</v>
       </c>
@@ -43104,7 +43105,7 @@
       </c>
       <c r="AP304" s="12"/>
     </row>
-    <row r="305" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="71">
         <v>46197</v>
       </c>
@@ -43226,7 +43227,7 @@
       </c>
       <c r="AP305" s="12"/>
     </row>
-    <row r="306" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="71">
         <v>46197</v>
       </c>
@@ -43358,7 +43359,7 @@
       </c>
       <c r="AP306" s="12"/>
     </row>
-    <row r="307" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="71">
         <v>46197</v>
       </c>
@@ -43482,7 +43483,7 @@
       </c>
       <c r="AP307" s="12"/>
     </row>
-    <row r="308" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="71">
         <v>46197</v>
       </c>
@@ -43616,7 +43617,7 @@
       </c>
       <c r="AP308" s="12"/>
     </row>
-    <row r="309" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="71">
         <v>46197</v>
       </c>
@@ -43746,7 +43747,7 @@
       </c>
       <c r="AP309" s="12"/>
     </row>
-    <row r="310" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="71">
         <v>46197</v>
       </c>
@@ -43876,7 +43877,7 @@
       </c>
       <c r="AP310" s="12"/>
     </row>
-    <row r="311" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="71">
         <v>46197</v>
       </c>
@@ -43998,7 +43999,7 @@
       </c>
       <c r="AP311" s="12"/>
     </row>
-    <row r="312" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="71">
         <v>46197</v>
       </c>
@@ -44120,7 +44121,7 @@
       </c>
       <c r="AP312" s="12"/>
     </row>
-    <row r="313" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="71">
         <v>46197</v>
       </c>
@@ -44242,7 +44243,7 @@
       </c>
       <c r="AP313" s="12"/>
     </row>
-    <row r="314" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="71">
         <v>46197</v>
       </c>
@@ -44370,7 +44371,7 @@
       </c>
       <c r="AP314" s="12"/>
     </row>
-    <row r="315" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="71">
         <v>46197</v>
       </c>
@@ -44496,7 +44497,7 @@
       </c>
       <c r="AP315" s="12"/>
     </row>
-    <row r="316" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="71">
         <v>46197</v>
       </c>
@@ -44618,7 +44619,7 @@
       </c>
       <c r="AP316" s="12"/>
     </row>
-    <row r="317" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="71">
         <v>46197</v>
       </c>
@@ -44740,7 +44741,7 @@
       </c>
       <c r="AP317" s="12"/>
     </row>
-    <row r="318" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="71">
         <v>46197</v>
       </c>
@@ -44862,7 +44863,7 @@
       </c>
       <c r="AP318" s="12"/>
     </row>
-    <row r="319" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="71">
         <v>46196</v>
       </c>
@@ -44992,7 +44993,7 @@
       </c>
       <c r="AP319" s="12"/>
     </row>
-    <row r="320" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="71">
         <v>46196</v>
       </c>
@@ -45122,7 +45123,7 @@
       </c>
       <c r="AP320" s="12"/>
     </row>
-    <row r="321" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="71">
         <v>46196</v>
       </c>
@@ -45252,7 +45253,7 @@
       </c>
       <c r="AP321" s="12"/>
     </row>
-    <row r="322" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="71">
         <v>46196</v>
       </c>
@@ -45382,7 +45383,7 @@
       </c>
       <c r="AP322" s="12"/>
     </row>
-    <row r="323" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="71">
         <v>46196</v>
       </c>
@@ -45512,7 +45513,7 @@
       </c>
       <c r="AP323" s="12"/>
     </row>
-    <row r="324" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="71">
         <v>46196</v>
       </c>
@@ -45642,7 +45643,7 @@
       </c>
       <c r="AP324" s="12"/>
     </row>
-    <row r="325" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="71">
         <v>46196</v>
       </c>
@@ -45772,7 +45773,7 @@
       </c>
       <c r="AP325" s="12"/>
     </row>
-    <row r="326" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="71">
         <v>46196</v>
       </c>
@@ -45902,7 +45903,7 @@
       </c>
       <c r="AP326" s="12"/>
     </row>
-    <row r="327" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="71">
         <v>46196</v>
       </c>
@@ -46032,7 +46033,7 @@
       </c>
       <c r="AP327" s="12"/>
     </row>
-    <row r="328" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="71">
         <v>46196</v>
       </c>
@@ -46424,7 +46425,7 @@
       </c>
       <c r="AP330" s="12"/>
     </row>
-    <row r="331" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="71">
         <v>46197</v>
       </c>
@@ -46554,7 +46555,7 @@
       </c>
       <c r="AP331" s="12"/>
     </row>
-    <row r="332" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="71">
         <v>46197</v>
       </c>
@@ -47070,7 +47071,7 @@
       </c>
       <c r="AP335" s="12"/>
     </row>
-    <row r="336" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="71">
         <v>46202</v>
       </c>
@@ -47198,7 +47199,7 @@
       </c>
       <c r="AP336" s="12"/>
     </row>
-    <row r="337" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="71">
         <v>46202</v>
       </c>
@@ -47322,7 +47323,7 @@
       </c>
       <c r="AP337" s="12"/>
     </row>
-    <row r="338" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="71">
         <v>46202</v>
       </c>
@@ -47448,7 +47449,7 @@
       </c>
       <c r="AP338" s="12"/>
     </row>
-    <row r="339" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="71">
         <v>46202</v>
       </c>
@@ -47572,7 +47573,7 @@
       </c>
       <c r="AP339" s="12"/>
     </row>
-    <row r="340" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="71">
         <v>46202</v>
       </c>
@@ -47706,7 +47707,7 @@
       </c>
       <c r="AP340" s="12"/>
     </row>
-    <row r="341" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="71">
         <v>46202</v>
       </c>
@@ -47836,7 +47837,7 @@
       </c>
       <c r="AP341" s="12"/>
     </row>
-    <row r="342" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="71">
         <v>46202</v>
       </c>
@@ -47966,7 +47967,7 @@
       </c>
       <c r="AP342" s="12"/>
     </row>
-    <row r="343" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="71">
         <v>46202</v>
       </c>
@@ -48094,7 +48095,7 @@
       </c>
       <c r="AP343" s="12"/>
     </row>
-    <row r="344" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="71">
         <v>46202</v>
       </c>
@@ -48224,7 +48225,7 @@
       </c>
       <c r="AP344" s="12"/>
     </row>
-    <row r="345" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="71">
         <v>46202</v>
       </c>
@@ -48354,7 +48355,7 @@
       </c>
       <c r="AP345" s="12"/>
     </row>
-    <row r="346" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="71">
         <v>46202</v>
       </c>
@@ -48484,7 +48485,7 @@
       </c>
       <c r="AP346" s="12"/>
     </row>
-    <row r="347" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="71">
         <v>46202</v>
       </c>
@@ -48612,7 +48613,7 @@
       </c>
       <c r="AP347" s="12"/>
     </row>
-    <row r="348" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="71">
         <v>46202</v>
       </c>
@@ -48736,7 +48737,7 @@
       </c>
       <c r="AP348" s="12"/>
     </row>
-    <row r="349" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="71">
         <v>46202</v>
       </c>
@@ -48864,7 +48865,7 @@
       </c>
       <c r="AP349" s="12"/>
     </row>
-    <row r="350" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="71">
         <v>46202</v>
       </c>
@@ -48994,7 +48995,7 @@
       </c>
       <c r="AP350" s="12"/>
     </row>
-    <row r="351" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="71">
         <v>46202</v>
       </c>
@@ -49124,7 +49125,7 @@
       </c>
       <c r="AP351" s="12"/>
     </row>
-    <row r="352" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="71">
         <v>46202</v>
       </c>
@@ -49244,7 +49245,7 @@
       </c>
       <c r="AP352" s="12"/>
     </row>
-    <row r="353" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="71">
         <v>46202</v>
       </c>
@@ -49374,7 +49375,7 @@
       </c>
       <c r="AP353" s="12"/>
     </row>
-    <row r="354" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="71">
         <v>46202</v>
       </c>
@@ -49504,7 +49505,7 @@
       </c>
       <c r="AP354" s="12"/>
     </row>
-    <row r="355" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="71">
         <v>46202</v>
       </c>
@@ -49636,7 +49637,7 @@
       </c>
       <c r="AP355" s="12"/>
     </row>
-    <row r="356" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="71">
         <v>46202</v>
       </c>
@@ -49768,7 +49769,7 @@
       </c>
       <c r="AP356" s="12"/>
     </row>
-    <row r="357" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="71">
         <v>46202</v>
       </c>
@@ -49900,7 +49901,7 @@
       </c>
       <c r="AP357" s="12"/>
     </row>
-    <row r="358" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="71">
         <v>46202</v>
       </c>
@@ -50032,7 +50033,7 @@
       </c>
       <c r="AP358" s="12"/>
     </row>
-    <row r="359" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="71">
         <v>46202</v>
       </c>
@@ -50164,7 +50165,7 @@
       </c>
       <c r="AP359" s="12"/>
     </row>
-    <row r="360" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="71">
         <v>46202</v>
       </c>
@@ -50296,7 +50297,7 @@
       </c>
       <c r="AP360" s="12"/>
     </row>
-    <row r="361" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="71">
         <v>46202</v>
       </c>
@@ -50812,7 +50813,7 @@
       </c>
       <c r="AP364" s="12"/>
     </row>
-    <row r="365" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="71">
         <v>46203</v>
       </c>
@@ -50938,7 +50939,7 @@
       </c>
       <c r="AP365" s="12"/>
     </row>
-    <row r="366" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="71">
         <v>46203</v>
       </c>
@@ -51060,7 +51061,7 @@
       </c>
       <c r="AP366" s="12"/>
     </row>
-    <row r="367" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="71">
         <v>46203</v>
       </c>
@@ -51188,7 +51189,7 @@
       </c>
       <c r="AP367" s="12"/>
     </row>
-    <row r="368" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="71">
         <v>46203</v>
       </c>
@@ -51314,7 +51315,7 @@
       </c>
       <c r="AP368" s="12"/>
     </row>
-    <row r="369" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="71">
         <v>46203</v>
       </c>
@@ -51438,7 +51439,7 @@
       </c>
       <c r="AP369" s="12"/>
     </row>
-    <row r="370" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="71">
         <v>46203</v>
       </c>
@@ -51560,7 +51561,7 @@
       </c>
       <c r="AP370" s="12"/>
     </row>
-    <row r="371" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="71">
         <v>46203</v>
       </c>
@@ -51690,7 +51691,7 @@
       </c>
       <c r="AP371" s="12"/>
     </row>
-    <row r="372" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="71">
         <v>46203</v>
       </c>
@@ -51814,7 +51815,7 @@
       </c>
       <c r="AP372" s="12"/>
     </row>
-    <row r="373" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="71">
         <v>46203</v>
       </c>
@@ -51938,7 +51939,7 @@
       </c>
       <c r="AP373" s="12"/>
     </row>
-    <row r="374" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="71">
         <v>46203</v>
       </c>
@@ -52066,7 +52067,7 @@
       </c>
       <c r="AP374" s="12"/>
     </row>
-    <row r="375" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="71">
         <v>46203</v>
       </c>
@@ -52190,7 +52191,7 @@
       </c>
       <c r="AP375" s="12"/>
     </row>
-    <row r="376" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="71">
         <v>46203</v>
       </c>
@@ -52314,7 +52315,7 @@
       </c>
       <c r="AP376" s="12"/>
     </row>
-    <row r="377" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="71">
         <v>46203</v>
       </c>
@@ -52438,7 +52439,7 @@
       </c>
       <c r="AP377" s="12"/>
     </row>
-    <row r="378" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="71">
         <v>46203</v>
       </c>
@@ -52568,7 +52569,7 @@
       </c>
       <c r="AP378" s="12"/>
     </row>
-    <row r="379" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="71">
         <v>46203</v>
       </c>
@@ -52700,7 +52701,7 @@
       </c>
       <c r="AP379" s="12"/>
     </row>
-    <row r="380" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="71">
         <v>46203</v>
       </c>
@@ -52828,7 +52829,7 @@
       </c>
       <c r="AP380" s="12"/>
     </row>
-    <row r="381" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="71">
         <v>46203</v>
       </c>
@@ -52954,7 +52955,7 @@
       </c>
       <c r="AP381" s="12"/>
     </row>
-    <row r="382" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="71">
         <v>46203</v>
       </c>
@@ -53082,7 +53083,7 @@
       </c>
       <c r="AP382" s="12"/>
     </row>
-    <row r="383" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="71">
         <v>46203</v>
       </c>
@@ -53214,7 +53215,7 @@
       </c>
       <c r="AP383" s="12"/>
     </row>
-    <row r="384" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="71">
         <v>46203</v>
       </c>
@@ -53346,7 +53347,7 @@
       </c>
       <c r="AP384" s="12"/>
     </row>
-    <row r="385" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="71">
         <v>46203</v>
       </c>
@@ -53474,7 +53475,7 @@
       </c>
       <c r="AP385" s="12"/>
     </row>
-    <row r="386" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="71">
         <v>46203</v>
       </c>
@@ -53596,7 +53597,7 @@
       </c>
       <c r="AP386" s="12"/>
     </row>
-    <row r="387" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="71">
         <v>46203</v>
       </c>
@@ -53722,7 +53723,7 @@
       </c>
       <c r="AP387" s="12"/>
     </row>
-    <row r="388" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="71">
         <v>46203</v>
       </c>
@@ -53846,7 +53847,7 @@
       </c>
       <c r="AP388" s="12"/>
     </row>
-    <row r="389" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" s="71">
         <v>46203</v>
       </c>
@@ -53968,7 +53969,7 @@
       </c>
       <c r="AP389" s="12"/>
     </row>
-    <row r="390" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" s="71">
         <v>46203</v>
       </c>
@@ -54090,7 +54091,7 @@
       </c>
       <c r="AP390" s="12"/>
     </row>
-    <row r="391" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" s="71">
         <v>46203</v>
       </c>
@@ -54212,7 +54213,7 @@
       </c>
       <c r="AP391" s="12"/>
     </row>
-    <row r="392" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" s="71">
         <v>46203</v>
       </c>
@@ -54334,7 +54335,7 @@
       </c>
       <c r="AP392" s="12"/>
     </row>
-    <row r="393" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="71">
         <v>46203</v>
       </c>
@@ -54456,7 +54457,7 @@
       </c>
       <c r="AP393" s="12"/>
     </row>
-    <row r="394" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" s="71">
         <v>46203</v>
       </c>
@@ -54578,7 +54579,7 @@
       </c>
       <c r="AP394" s="12"/>
     </row>
-    <row r="395" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="71">
         <v>46203</v>
       </c>
@@ -54708,7 +54709,7 @@
       </c>
       <c r="AP395" s="12"/>
     </row>
-    <row r="396" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="71">
         <v>46203</v>
       </c>
@@ -54838,7 +54839,7 @@
       </c>
       <c r="AP396" s="12"/>
     </row>
-    <row r="397" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="71">
         <v>46203</v>
       </c>
@@ -54968,7 +54969,7 @@
       </c>
       <c r="AP397" s="12"/>
     </row>
-    <row r="398" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="71">
         <v>46203</v>
       </c>
@@ -55098,7 +55099,7 @@
       </c>
       <c r="AP398" s="12"/>
     </row>
-    <row r="399" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="71">
         <v>46203</v>
       </c>
@@ -55225,7 +55226,7 @@
       </c>
       <c r="AP399" s="12"/>
     </row>
-    <row r="400" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="71">
         <v>46203</v>
       </c>
@@ -55352,7 +55353,7 @@
       </c>
       <c r="AP400" s="12"/>
     </row>
-    <row r="401" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="71">
         <v>46203</v>
       </c>
@@ -55479,7 +55480,7 @@
       </c>
       <c r="AP401" s="12"/>
     </row>
-    <row r="402" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="71">
         <v>46203</v>
       </c>
@@ -55606,7 +55607,7 @@
       </c>
       <c r="AP402" s="12"/>
     </row>
-    <row r="403" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" s="71">
         <v>46203</v>
       </c>
@@ -55733,7 +55734,7 @@
       </c>
       <c r="AP403" s="12"/>
     </row>
-    <row r="404" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="71">
         <v>46203</v>
       </c>
@@ -55860,7 +55861,7 @@
       </c>
       <c r="AP404" s="12"/>
     </row>
-    <row r="405" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" s="71">
         <v>46203</v>
       </c>
@@ -55987,7 +55988,7 @@
       </c>
       <c r="AP405" s="12"/>
     </row>
-    <row r="406" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" s="17"/>
       <c r="C406" s="18"/>
       <c r="E406" s="6"/>
@@ -56084,7 +56085,7 @@
       </c>
       <c r="AP406" s="12"/>
     </row>
-    <row r="407" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="17"/>
       <c r="C407" s="18"/>
       <c r="E407" s="6"/>
@@ -56181,7 +56182,7 @@
       </c>
       <c r="AP407" s="12"/>
     </row>
-    <row r="408" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" s="17"/>
       <c r="C408" s="18"/>
       <c r="E408" s="6"/>
@@ -56278,7 +56279,7 @@
       </c>
       <c r="AP408" s="12"/>
     </row>
-    <row r="409" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="17"/>
       <c r="C409" s="18"/>
       <c r="E409" s="6"/>
@@ -56375,7 +56376,7 @@
       </c>
       <c r="AP409" s="12"/>
     </row>
-    <row r="410" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="17"/>
       <c r="C410" s="18"/>
       <c r="E410" s="6"/>
@@ -56472,7 +56473,7 @@
       </c>
       <c r="AP410" s="12"/>
     </row>
-    <row r="411" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="17"/>
       <c r="C411" s="18"/>
       <c r="E411" s="6"/>
@@ -56569,7 +56570,7 @@
       </c>
       <c r="AP411" s="12"/>
     </row>
-    <row r="412" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="17"/>
       <c r="C412" s="18"/>
       <c r="E412" s="6"/>
@@ -56666,7 +56667,7 @@
       </c>
       <c r="AP412" s="12"/>
     </row>
-    <row r="413" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="17"/>
       <c r="C413" s="18"/>
       <c r="E413" s="6"/>
@@ -56763,7 +56764,7 @@
       </c>
       <c r="AP413" s="12"/>
     </row>
-    <row r="414" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="17"/>
       <c r="C414" s="18"/>
       <c r="E414" s="6"/>
@@ -56860,7 +56861,7 @@
       </c>
       <c r="AP414" s="12"/>
     </row>
-    <row r="415" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="17"/>
       <c r="C415" s="18"/>
       <c r="E415" s="6"/>
@@ -56957,7 +56958,7 @@
       </c>
       <c r="AP415" s="12"/>
     </row>
-    <row r="416" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="17"/>
       <c r="C416" s="18"/>
       <c r="E416" s="6"/>
@@ -57054,7 +57055,7 @@
       </c>
       <c r="AP416" s="12"/>
     </row>
-    <row r="417" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="17"/>
       <c r="C417" s="18"/>
       <c r="E417" s="6"/>
@@ -57151,7 +57152,7 @@
       </c>
       <c r="AP417" s="12"/>
     </row>
-    <row r="418" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="17"/>
       <c r="C418" s="18"/>
       <c r="E418" s="6"/>
@@ -57248,7 +57249,7 @@
       </c>
       <c r="AP418" s="12"/>
     </row>
-    <row r="419" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" s="17"/>
       <c r="C419" s="18"/>
       <c r="E419" s="6"/>
@@ -57345,7 +57346,7 @@
       </c>
       <c r="AP419" s="12"/>
     </row>
-    <row r="420" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" s="17"/>
       <c r="C420" s="18"/>
       <c r="E420" s="6"/>
@@ -57442,7 +57443,7 @@
       </c>
       <c r="AP420" s="12"/>
     </row>
-    <row r="421" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" s="17"/>
       <c r="C421" s="18"/>
       <c r="E421" s="6"/>
@@ -57539,7 +57540,7 @@
       </c>
       <c r="AP421" s="12"/>
     </row>
-    <row r="422" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" s="17"/>
       <c r="C422" s="18"/>
       <c r="E422" s="6"/>
@@ -57636,7 +57637,7 @@
       </c>
       <c r="AP422" s="12"/>
     </row>
-    <row r="423" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" s="17"/>
       <c r="C423" s="18"/>
       <c r="E423" s="6"/>
@@ -57733,7 +57734,7 @@
       </c>
       <c r="AP423" s="12"/>
     </row>
-    <row r="424" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" s="17"/>
       <c r="C424" s="18"/>
       <c r="E424" s="6"/>
@@ -57830,7 +57831,7 @@
       </c>
       <c r="AP424" s="12"/>
     </row>
-    <row r="425" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" s="6"/>
       <c r="C425" s="6"/>
       <c r="E425" s="6"/>
@@ -58144,6 +58145,46 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP425" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="LMT"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="24/7 Mart"/>
+        <filter val="4 Reason"/>
+        <filter val="Al Fatah"/>
+        <filter val="Al Raheem Iqbal Town"/>
+        <filter val="Al Raheem Wapda Town"/>
+        <filter val="Al-Fatah"/>
+        <filter val="Asgher Store"/>
+        <filter val="Aslam Super Mart"/>
+        <filter val="Clinix"/>
+        <filter val="Crown"/>
+        <filter val="Euro Store"/>
+        <filter val="Galaxy Super Market"/>
+        <filter val="Jalal Sons"/>
+        <filter val="Jalal sons Askari 10"/>
+        <filter val="Jalal Sons Bahria Orchard"/>
+        <filter val="Jalal Sons Behria Orchard"/>
+        <filter val="Jalal Sons Lake City"/>
+        <filter val="Jalal sons main market"/>
+        <filter val="Jalal Sons phase 5"/>
+        <filter val="Lake City Mart"/>
+        <filter val="MB Traders"/>
+        <filter val="Ms Traders (Risen)"/>
+        <filter val="Pak Madina (Jharawala)"/>
+        <filter val="Rafaqat &amp; Sons"/>
+        <filter val="Rainbow BT"/>
+        <filter val="Rainbow Cash &amp; Carry"/>
+        <filter val="Rehman Garden (Risen)"/>
+        <filter val="Risan Askari 11"/>
+        <filter val="Sana Cash &amp; Carry"/>
+        <filter val="Shehwar Mega Mart"/>
+        <filter val="Swera Store"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="10" showButton="0"/>
     <filterColumn colId="11" showButton="0"/>
     <filterColumn colId="12" showButton="0"/>
@@ -58158,13 +58199,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -58177,14 +58219,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/june 2026/STT Report JUNE 2026.xlsx
+++ b/june 2026/STT Report JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\june 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3161698C-80E1-4F31-AA46-D6BBA50ED755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76114F2-B135-48C6-A740-B5FC3A09C778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -2610,22 +2610,41 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="15" xfId="4" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="4" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2637,11 +2656,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2660,25 +2679,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="15" xfId="4" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="4" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3041,114 +3041,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="106" t="s">
+      <c r="A1" s="114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="107" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="107" t="s">
+      <c r="C1" s="111" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="107" t="s">
+      <c r="E1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="107" t="s">
+      <c r="F1" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="G1" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="107" t="s">
+      <c r="H1" s="111" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="106" t="s">
+      <c r="K1" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="111" t="s">
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="108" t="s">
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="117" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="110" t="s">
+      <c r="T1" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110" t="s">
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="104" t="s">
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="104" t="s">
+      <c r="AC1" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="104" t="s">
+      <c r="AD1" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="104" t="s">
+      <c r="AE1" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="104" t="s">
+      <c r="AF1" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="104" t="s">
+      <c r="AG1" s="115" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="104" t="s">
+      <c r="AI1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="104" t="s">
+      <c r="AJ1" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="104" t="s">
+      <c r="AK1" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="104" t="s">
+      <c r="AL1" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="104" t="s">
+      <c r="AM1" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="102" t="s">
+      <c r="AN1" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="102" t="s">
+      <c r="AO1" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="104" t="s">
+      <c r="AP1" s="115" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="107"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="111"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -3179,7 +3179,7 @@
       <c r="R2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="118"/>
       <c r="T2" s="4" t="s">
         <v>352</v>
       </c>
@@ -3204,23 +3204,23 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="105"/>
-      <c r="AC2" s="105"/>
-      <c r="AD2" s="105"/>
-      <c r="AE2" s="105"/>
-      <c r="AF2" s="105"/>
-      <c r="AG2" s="105"/>
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="116"/>
+      <c r="AE2" s="116"/>
+      <c r="AF2" s="116"/>
+      <c r="AG2" s="116"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="105"/>
-      <c r="AJ2" s="105"/>
-      <c r="AK2" s="105"/>
-      <c r="AL2" s="105"/>
-      <c r="AM2" s="105"/>
-      <c r="AN2" s="103"/>
-      <c r="AO2" s="103"/>
-      <c r="AP2" s="105"/>
+      <c r="AI2" s="116"/>
+      <c r="AJ2" s="116"/>
+      <c r="AK2" s="116"/>
+      <c r="AL2" s="116"/>
+      <c r="AM2" s="116"/>
+      <c r="AN2" s="121"/>
+      <c r="AO2" s="121"/>
+      <c r="AP2" s="116"/>
     </row>
     <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="70">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AP38" s="12"/>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="70">
         <v>46209</v>
       </c>
@@ -8091,7 +8091,7 @@
       <c r="F39" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G39" s="125" t="s">
+      <c r="G39" s="108" t="s">
         <v>209</v>
       </c>
       <c r="H39" s="74" t="s">
@@ -8100,29 +8100,29 @@
       <c r="I39" s="77" t="s">
         <v>142</v>
       </c>
-      <c r="J39" s="119">
+      <c r="J39" s="102">
         <v>800</v>
       </c>
-      <c r="K39" s="120">
+      <c r="K39" s="103">
         <v>800</v>
       </c>
-      <c r="L39" s="120">
+      <c r="L39" s="103">
         <v>800</v>
       </c>
-      <c r="M39" s="120">
+      <c r="M39" s="103">
         <v>400</v>
       </c>
       <c r="N39" s="8">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
-      <c r="O39" s="123">
+      <c r="O39" s="106">
         <v>800</v>
       </c>
-      <c r="P39" s="123">
+      <c r="P39" s="106">
         <v>800</v>
       </c>
-      <c r="Q39" s="122">
+      <c r="Q39" s="105">
         <v>800</v>
       </c>
       <c r="R39" s="8">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="AP39" s="12"/>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="70">
         <v>46209</v>
       </c>
@@ -8225,7 +8225,7 @@
       <c r="F40" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G40" s="125" t="s">
+      <c r="G40" s="108" t="s">
         <v>210</v>
       </c>
       <c r="H40" s="74" t="s">
@@ -8234,29 +8234,29 @@
       <c r="I40" s="77" t="s">
         <v>142</v>
       </c>
-      <c r="J40" s="119">
+      <c r="J40" s="102">
         <v>80</v>
       </c>
-      <c r="K40" s="120">
+      <c r="K40" s="103">
         <v>80</v>
       </c>
-      <c r="L40" s="120">
+      <c r="L40" s="103">
         <v>80</v>
       </c>
-      <c r="M40" s="120">
+      <c r="M40" s="103">
         <v>80</v>
       </c>
       <c r="N40" s="8">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="O40" s="123">
+      <c r="O40" s="106">
         <v>80</v>
       </c>
-      <c r="P40" s="123">
+      <c r="P40" s="106">
         <v>80</v>
       </c>
-      <c r="Q40" s="122">
+      <c r="Q40" s="105">
         <v>80</v>
       </c>
       <c r="R40" s="8">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="AP40" s="12"/>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="70">
         <v>46209</v>
       </c>
@@ -8359,7 +8359,7 @@
       <c r="F41" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G41" s="125" t="s">
+      <c r="G41" s="108" t="s">
         <v>211</v>
       </c>
       <c r="H41" s="74" t="s">
@@ -8368,29 +8368,29 @@
       <c r="I41" s="77" t="s">
         <v>142</v>
       </c>
-      <c r="J41" s="119">
+      <c r="J41" s="102">
         <v>200</v>
       </c>
-      <c r="K41" s="120">
+      <c r="K41" s="103">
         <v>200</v>
       </c>
-      <c r="L41" s="120">
+      <c r="L41" s="103">
         <v>200</v>
       </c>
-      <c r="M41" s="120">
+      <c r="M41" s="103">
         <v>270</v>
       </c>
       <c r="N41" s="8">
         <f t="shared" si="1"/>
         <v>670</v>
       </c>
-      <c r="O41" s="123">
+      <c r="O41" s="106">
         <v>200</v>
       </c>
-      <c r="P41" s="123">
+      <c r="P41" s="106">
         <v>200</v>
       </c>
-      <c r="Q41" s="122">
+      <c r="Q41" s="105">
         <v>200</v>
       </c>
       <c r="R41" s="8">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="AP44" s="12"/>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="70">
         <v>46211</v>
       </c>
@@ -8889,7 +8889,7 @@
       <c r="F45" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G45" s="125" t="s">
+      <c r="G45" s="108" t="s">
         <v>213</v>
       </c>
       <c r="H45" s="74" t="s">
@@ -8898,27 +8898,27 @@
       <c r="I45" s="77" t="s">
         <v>215</v>
       </c>
-      <c r="J45" s="119"/>
-      <c r="K45" s="121">
-        <v>0</v>
-      </c>
-      <c r="L45" s="120">
-        <v>0</v>
-      </c>
-      <c r="M45" s="120">
+      <c r="J45" s="102"/>
+      <c r="K45" s="104">
+        <v>0</v>
+      </c>
+      <c r="L45" s="103">
+        <v>0</v>
+      </c>
+      <c r="M45" s="103">
         <v>0</v>
       </c>
       <c r="N45" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O45" s="123">
+      <c r="O45" s="106">
         <v>560</v>
       </c>
-      <c r="P45" s="120">
+      <c r="P45" s="103">
         <v>560</v>
       </c>
-      <c r="Q45" s="122">
+      <c r="Q45" s="105">
         <v>880</v>
       </c>
       <c r="R45" s="8">
@@ -9021,7 +9021,7 @@
       <c r="F46" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G46" s="125" t="s">
+      <c r="G46" s="108" t="s">
         <v>214</v>
       </c>
       <c r="H46" s="74" t="s">
@@ -9030,27 +9030,27 @@
       <c r="I46" s="77" t="s">
         <v>216</v>
       </c>
-      <c r="J46" s="119"/>
-      <c r="K46" s="121">
+      <c r="J46" s="102"/>
+      <c r="K46" s="104">
         <v>1200</v>
       </c>
-      <c r="L46" s="120">
+      <c r="L46" s="103">
         <v>1200</v>
       </c>
-      <c r="M46" s="120">
+      <c r="M46" s="103">
         <v>1800</v>
       </c>
       <c r="N46" s="8">
         <f t="shared" si="1"/>
         <v>4200</v>
       </c>
-      <c r="O46" s="123">
+      <c r="O46" s="106">
         <v>2400</v>
       </c>
-      <c r="P46" s="120">
+      <c r="P46" s="103">
         <v>1800</v>
       </c>
-      <c r="Q46" s="122">
+      <c r="Q46" s="105">
         <v>1800</v>
       </c>
       <c r="R46" s="8">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AP60" s="12"/>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="70">
         <v>46212</v>
       </c>
@@ -11007,7 +11007,7 @@
       <c r="F61" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G61" s="125" t="s">
+      <c r="G61" s="108" t="s">
         <v>217</v>
       </c>
       <c r="H61" s="74" t="s">
@@ -11016,27 +11016,27 @@
       <c r="I61" s="77" t="s">
         <v>219</v>
       </c>
-      <c r="J61" s="119"/>
-      <c r="K61" s="120">
-        <v>0</v>
-      </c>
-      <c r="L61" s="120">
-        <v>40</v>
-      </c>
-      <c r="M61" s="120">
+      <c r="J61" s="102"/>
+      <c r="K61" s="103">
+        <v>0</v>
+      </c>
+      <c r="L61" s="103">
+        <v>40</v>
+      </c>
+      <c r="M61" s="103">
         <v>70</v>
       </c>
       <c r="N61" s="8">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
-      <c r="O61" s="123">
-        <v>40</v>
-      </c>
-      <c r="P61" s="122">
-        <v>40</v>
-      </c>
-      <c r="Q61" s="124">
+      <c r="O61" s="106">
+        <v>40</v>
+      </c>
+      <c r="P61" s="105">
+        <v>40</v>
+      </c>
+      <c r="Q61" s="107">
         <v>40</v>
       </c>
       <c r="R61" s="8">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="AP61" s="12"/>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="70">
         <v>46212</v>
       </c>
@@ -11139,7 +11139,7 @@
       <c r="F62" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G62" s="125" t="s">
+      <c r="G62" s="108" t="s">
         <v>218</v>
       </c>
       <c r="H62" s="74" t="s">
@@ -11148,27 +11148,27 @@
       <c r="I62" s="77" t="s">
         <v>552</v>
       </c>
-      <c r="J62" s="119"/>
-      <c r="K62" s="120">
+      <c r="J62" s="102"/>
+      <c r="K62" s="103">
         <v>400</v>
       </c>
-      <c r="L62" s="120">
+      <c r="L62" s="103">
         <v>200</v>
       </c>
-      <c r="M62" s="120">
+      <c r="M62" s="103">
         <v>40</v>
       </c>
       <c r="N62" s="8">
         <f t="shared" si="1"/>
         <v>640</v>
       </c>
-      <c r="O62" s="123">
+      <c r="O62" s="106">
         <v>400</v>
       </c>
-      <c r="P62" s="122">
+      <c r="P62" s="105">
         <v>200</v>
       </c>
-      <c r="Q62" s="124">
+      <c r="Q62" s="107">
         <v>400</v>
       </c>
       <c r="R62" s="8">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="AP76" s="12"/>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="70">
         <v>46183</v>
       </c>
@@ -13147,7 +13147,7 @@
       <c r="F77" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G77" s="125" t="s">
+      <c r="G77" s="108" t="s">
         <v>220</v>
       </c>
       <c r="H77" s="74" t="s">
@@ -13156,27 +13156,27 @@
       <c r="I77" s="77" t="s">
         <v>223</v>
       </c>
-      <c r="J77" s="119"/>
-      <c r="K77" s="122">
+      <c r="J77" s="102"/>
+      <c r="K77" s="105">
         <v>240</v>
       </c>
-      <c r="L77" s="122">
+      <c r="L77" s="105">
         <v>240</v>
       </c>
-      <c r="M77" s="122">
+      <c r="M77" s="105">
         <v>80</v>
       </c>
       <c r="N77" s="8">
         <f t="shared" si="32"/>
         <v>560</v>
       </c>
-      <c r="O77" s="124">
+      <c r="O77" s="107">
         <v>240</v>
       </c>
-      <c r="P77" s="124">
+      <c r="P77" s="107">
         <v>240</v>
       </c>
-      <c r="Q77" s="124">
+      <c r="Q77" s="107">
         <v>600</v>
       </c>
       <c r="R77" s="8">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="AP77" s="12"/>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="70">
         <v>46183</v>
       </c>
@@ -13279,7 +13279,7 @@
       <c r="F78" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G78" s="125" t="s">
+      <c r="G78" s="108" t="s">
         <v>221</v>
       </c>
       <c r="H78" s="74" t="s">
@@ -13288,27 +13288,27 @@
       <c r="I78" s="77" t="s">
         <v>224</v>
       </c>
-      <c r="J78" s="119"/>
-      <c r="K78" s="122">
-        <v>0</v>
-      </c>
-      <c r="L78" s="122">
-        <v>0</v>
-      </c>
-      <c r="M78" s="122">
+      <c r="J78" s="102"/>
+      <c r="K78" s="105">
+        <v>0</v>
+      </c>
+      <c r="L78" s="105">
+        <v>0</v>
+      </c>
+      <c r="M78" s="105">
         <v>80</v>
       </c>
       <c r="N78" s="8">
         <f t="shared" si="32"/>
         <v>80</v>
       </c>
-      <c r="O78" s="124">
+      <c r="O78" s="107">
         <v>80</v>
       </c>
-      <c r="P78" s="124">
+      <c r="P78" s="107">
         <v>80</v>
       </c>
-      <c r="Q78" s="124">
+      <c r="Q78" s="107">
         <v>80</v>
       </c>
       <c r="R78" s="8">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="AP78" s="12"/>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="70">
         <v>46183</v>
       </c>
@@ -13411,7 +13411,7 @@
       <c r="F79" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G79" s="125" t="s">
+      <c r="G79" s="108" t="s">
         <v>222</v>
       </c>
       <c r="H79" s="74" t="s">
@@ -13420,27 +13420,27 @@
       <c r="I79" s="77" t="s">
         <v>553</v>
       </c>
-      <c r="J79" s="119"/>
-      <c r="K79" s="122">
+      <c r="J79" s="102"/>
+      <c r="K79" s="105">
         <v>80</v>
       </c>
-      <c r="L79" s="122">
+      <c r="L79" s="105">
         <v>80</v>
       </c>
-      <c r="M79" s="122">
+      <c r="M79" s="105">
         <v>20</v>
       </c>
       <c r="N79" s="8">
         <f t="shared" si="32"/>
         <v>180</v>
       </c>
-      <c r="O79" s="124">
+      <c r="O79" s="107">
         <v>80</v>
       </c>
-      <c r="P79" s="124">
-        <v>40</v>
-      </c>
-      <c r="Q79" s="124">
+      <c r="P79" s="107">
+        <v>40</v>
+      </c>
+      <c r="Q79" s="107">
         <v>80</v>
       </c>
       <c r="R79" s="8">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="AP91" s="12"/>
     </row>
-    <row r="92" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="70">
         <v>46184</v>
       </c>
@@ -15151,7 +15151,7 @@
       <c r="F92" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G92" s="125" t="s">
+      <c r="G92" s="108" t="s">
         <v>226</v>
       </c>
       <c r="H92" s="74" t="s">
@@ -15160,27 +15160,27 @@
       <c r="I92" s="77" t="s">
         <v>228</v>
       </c>
-      <c r="J92" s="119">
+      <c r="J92" s="102">
         <v>4</v>
       </c>
-      <c r="K92" s="123">
-        <v>40</v>
-      </c>
-      <c r="L92" s="120"/>
-      <c r="M92" s="120">
+      <c r="K92" s="106">
+        <v>40</v>
+      </c>
+      <c r="L92" s="103"/>
+      <c r="M92" s="103">
         <v>40</v>
       </c>
       <c r="N92" s="8">
         <f t="shared" si="32"/>
         <v>80</v>
       </c>
-      <c r="O92" s="123">
-        <v>0</v>
-      </c>
-      <c r="P92" s="120">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="120">
+      <c r="O92" s="106">
+        <v>0</v>
+      </c>
+      <c r="P92" s="103">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="103">
         <v>80</v>
       </c>
       <c r="R92" s="8">
@@ -15283,7 +15283,7 @@
       <c r="F93" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G93" s="125" t="s">
+      <c r="G93" s="108" t="s">
         <v>214</v>
       </c>
       <c r="H93" s="74" t="s">
@@ -15292,29 +15292,29 @@
       <c r="I93" s="77" t="s">
         <v>229</v>
       </c>
-      <c r="J93" s="119">
-        <v>0</v>
-      </c>
-      <c r="K93" s="123">
+      <c r="J93" s="102">
+        <v>0</v>
+      </c>
+      <c r="K93" s="106">
         <v>600</v>
       </c>
-      <c r="L93" s="120">
+      <c r="L93" s="103">
         <v>597</v>
       </c>
-      <c r="M93" s="120">
+      <c r="M93" s="103">
         <v>820</v>
       </c>
       <c r="N93" s="8">
         <f t="shared" si="32"/>
         <v>2017</v>
       </c>
-      <c r="O93" s="123">
+      <c r="O93" s="106">
         <v>1597</v>
       </c>
-      <c r="P93" s="120">
+      <c r="P93" s="103">
         <v>1184</v>
       </c>
-      <c r="Q93" s="120">
+      <c r="Q93" s="103">
         <v>1199</v>
       </c>
       <c r="R93" s="8">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="AP93" s="12"/>
     </row>
-    <row r="94" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="70">
         <v>46184</v>
       </c>
@@ -15417,7 +15417,7 @@
       <c r="F94" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G94" s="125" t="s">
+      <c r="G94" s="108" t="s">
         <v>227</v>
       </c>
       <c r="H94" s="74" t="s">
@@ -15426,23 +15426,23 @@
       <c r="I94" s="77" t="s">
         <v>142</v>
       </c>
-      <c r="J94" s="119"/>
-      <c r="K94" s="123"/>
-      <c r="L94" s="120"/>
-      <c r="M94" s="120">
+      <c r="J94" s="102"/>
+      <c r="K94" s="106"/>
+      <c r="L94" s="103"/>
+      <c r="M94" s="103">
         <v>60</v>
       </c>
       <c r="N94" s="8">
         <f t="shared" si="32"/>
         <v>60</v>
       </c>
-      <c r="O94" s="123">
-        <v>40</v>
-      </c>
-      <c r="P94" s="120">
-        <v>40</v>
-      </c>
-      <c r="Q94" s="120">
+      <c r="O94" s="106">
+        <v>40</v>
+      </c>
+      <c r="P94" s="103">
+        <v>40</v>
+      </c>
+      <c r="Q94" s="103">
         <v>40</v>
       </c>
       <c r="R94" s="8">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="AP94" s="12"/>
     </row>
-    <row r="95" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="70">
         <v>46184</v>
       </c>
@@ -15545,7 +15545,7 @@
       <c r="F95" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="G95" s="125" t="s">
+      <c r="G95" s="108" t="s">
         <v>143</v>
       </c>
       <c r="H95" s="74" t="s">
@@ -15554,27 +15554,27 @@
       <c r="I95" s="77" t="s">
         <v>142</v>
       </c>
-      <c r="J95" s="119"/>
-      <c r="K95" s="123">
-        <v>40</v>
-      </c>
-      <c r="L95" s="120">
-        <v>40</v>
-      </c>
-      <c r="M95" s="120">
+      <c r="J95" s="102"/>
+      <c r="K95" s="106">
+        <v>40</v>
+      </c>
+      <c r="L95" s="103">
+        <v>40</v>
+      </c>
+      <c r="M95" s="103">
         <v>40</v>
       </c>
       <c r="N95" s="8">
         <f t="shared" si="32"/>
         <v>120</v>
       </c>
-      <c r="O95" s="123">
-        <v>40</v>
-      </c>
-      <c r="P95" s="120">
-        <v>40</v>
-      </c>
-      <c r="Q95" s="120">
+      <c r="O95" s="106">
+        <v>40</v>
+      </c>
+      <c r="P95" s="103">
+        <v>40</v>
+      </c>
+      <c r="Q95" s="103">
         <v>40</v>
       </c>
       <c r="R95" s="8">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="AP135" s="12"/>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="70">
         <v>46189</v>
       </c>
@@ -21025,7 +21025,7 @@
       <c r="F136" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G136" s="126" t="s">
+      <c r="G136" s="109" t="s">
         <v>241</v>
       </c>
       <c r="H136" s="72" t="s">
@@ -21034,29 +21034,29 @@
       <c r="I136" s="62" t="s">
         <v>247</v>
       </c>
-      <c r="J136" s="119">
+      <c r="J136" s="102">
         <v>80</v>
       </c>
-      <c r="K136" s="124">
+      <c r="K136" s="107">
         <v>80</v>
       </c>
-      <c r="L136" s="124">
+      <c r="L136" s="107">
         <v>80</v>
       </c>
-      <c r="M136" s="124">
+      <c r="M136" s="107">
         <v>80</v>
       </c>
       <c r="N136" s="8">
         <f t="shared" si="55"/>
         <v>240</v>
       </c>
-      <c r="O136" s="122">
+      <c r="O136" s="105">
         <v>80</v>
       </c>
-      <c r="P136" s="124">
+      <c r="P136" s="107">
         <v>80</v>
       </c>
-      <c r="Q136" s="122">
+      <c r="Q136" s="105">
         <v>80</v>
       </c>
       <c r="R136" s="8">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="AP136" s="12"/>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="70">
         <v>46189</v>
       </c>
@@ -21159,7 +21159,7 @@
       <c r="F137" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G137" s="126" t="s">
+      <c r="G137" s="109" t="s">
         <v>242</v>
       </c>
       <c r="H137" s="72" t="s">
@@ -21168,29 +21168,29 @@
       <c r="I137" s="62" t="s">
         <v>247</v>
       </c>
-      <c r="J137" s="119">
+      <c r="J137" s="102">
         <v>120</v>
       </c>
-      <c r="K137" s="122">
+      <c r="K137" s="105">
         <v>120</v>
       </c>
-      <c r="L137" s="124">
+      <c r="L137" s="107">
         <v>120</v>
       </c>
-      <c r="M137" s="122">
+      <c r="M137" s="105">
         <v>80</v>
       </c>
       <c r="N137" s="8">
         <f t="shared" si="55"/>
         <v>320</v>
       </c>
-      <c r="O137" s="122">
+      <c r="O137" s="105">
         <v>120</v>
       </c>
-      <c r="P137" s="122">
+      <c r="P137" s="105">
         <v>120</v>
       </c>
-      <c r="Q137" s="122">
+      <c r="Q137" s="105">
         <v>120</v>
       </c>
       <c r="R137" s="8">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="AP160" s="12"/>
     </row>
-    <row r="161" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="70">
         <v>46190</v>
       </c>
@@ -24369,7 +24369,7 @@
       <c r="F161" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G161" s="126" t="s">
+      <c r="G161" s="109" t="s">
         <v>278</v>
       </c>
       <c r="H161" s="72" t="s">
@@ -24378,27 +24378,27 @@
       <c r="I161" s="62" t="s">
         <v>236</v>
       </c>
-      <c r="J161" s="119"/>
-      <c r="K161" s="124">
-        <v>40</v>
-      </c>
-      <c r="L161" s="124">
-        <v>40</v>
-      </c>
-      <c r="M161" s="124">
+      <c r="J161" s="102"/>
+      <c r="K161" s="107">
+        <v>40</v>
+      </c>
+      <c r="L161" s="107">
+        <v>40</v>
+      </c>
+      <c r="M161" s="107">
         <v>80</v>
       </c>
       <c r="N161" s="8">
         <f t="shared" si="55"/>
         <v>160</v>
       </c>
-      <c r="O161" s="122">
-        <v>40</v>
-      </c>
-      <c r="P161" s="122">
-        <v>0</v>
-      </c>
-      <c r="Q161" s="122">
+      <c r="O161" s="105">
+        <v>40</v>
+      </c>
+      <c r="P161" s="105">
+        <v>0</v>
+      </c>
+      <c r="Q161" s="105">
         <v>80</v>
       </c>
       <c r="R161" s="8">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="AP161" s="12"/>
     </row>
-    <row r="162" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="70">
         <v>46190</v>
       </c>
@@ -24501,7 +24501,7 @@
       <c r="F162" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G162" s="126" t="s">
+      <c r="G162" s="109" t="s">
         <v>210</v>
       </c>
       <c r="H162" s="72" t="s">
@@ -24510,27 +24510,27 @@
       <c r="I162" s="62" t="s">
         <v>294</v>
       </c>
-      <c r="J162" s="119"/>
-      <c r="K162" s="124">
+      <c r="J162" s="102"/>
+      <c r="K162" s="107">
         <v>80</v>
       </c>
-      <c r="L162" s="124">
+      <c r="L162" s="107">
         <v>80</v>
       </c>
-      <c r="M162" s="124">
+      <c r="M162" s="107">
         <v>40</v>
       </c>
       <c r="N162" s="8">
         <f t="shared" si="55"/>
         <v>200</v>
       </c>
-      <c r="O162" s="122">
+      <c r="O162" s="105">
         <v>80</v>
       </c>
-      <c r="P162" s="122">
+      <c r="P162" s="105">
         <v>80</v>
       </c>
-      <c r="Q162" s="124">
+      <c r="Q162" s="107">
         <v>200</v>
       </c>
       <c r="R162" s="8">
@@ -24614,7 +24614,7 @@
       </c>
       <c r="AP162" s="12"/>
     </row>
-    <row r="163" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="70">
         <v>46190</v>
       </c>
@@ -24633,7 +24633,7 @@
       <c r="F163" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G163" s="126" t="s">
+      <c r="G163" s="109" t="s">
         <v>279</v>
       </c>
       <c r="H163" s="72" t="s">
@@ -24642,27 +24642,27 @@
       <c r="I163" s="62" t="s">
         <v>295</v>
       </c>
-      <c r="J163" s="119"/>
-      <c r="K163" s="124">
+      <c r="J163" s="102"/>
+      <c r="K163" s="107">
         <v>80</v>
       </c>
-      <c r="L163" s="124">
+      <c r="L163" s="107">
         <v>80</v>
       </c>
-      <c r="M163" s="124">
+      <c r="M163" s="107">
         <v>80</v>
       </c>
       <c r="N163" s="8">
         <f t="shared" si="55"/>
         <v>240</v>
       </c>
-      <c r="O163" s="122">
+      <c r="O163" s="105">
         <v>80</v>
       </c>
-      <c r="P163" s="122">
+      <c r="P163" s="105">
         <v>80</v>
       </c>
-      <c r="Q163" s="122">
+      <c r="Q163" s="105">
         <v>80</v>
       </c>
       <c r="R163" s="8">
@@ -24746,7 +24746,7 @@
       </c>
       <c r="AP163" s="12"/>
     </row>
-    <row r="164" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="70">
         <v>46190</v>
       </c>
@@ -24765,7 +24765,7 @@
       <c r="F164" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G164" s="126" t="s">
+      <c r="G164" s="109" t="s">
         <v>280</v>
       </c>
       <c r="H164" s="72" t="s">
@@ -24774,27 +24774,27 @@
       <c r="I164" s="62" t="s">
         <v>293</v>
       </c>
-      <c r="J164" s="119"/>
-      <c r="K164" s="124">
-        <v>40</v>
-      </c>
-      <c r="L164" s="122">
-        <v>40</v>
-      </c>
-      <c r="M164" s="122">
+      <c r="J164" s="102"/>
+      <c r="K164" s="107">
+        <v>40</v>
+      </c>
+      <c r="L164" s="105">
+        <v>40</v>
+      </c>
+      <c r="M164" s="105">
         <v>80</v>
       </c>
       <c r="N164" s="8">
         <f t="shared" si="55"/>
         <v>160</v>
       </c>
-      <c r="O164" s="122">
+      <c r="O164" s="105">
         <v>80</v>
       </c>
-      <c r="P164" s="122">
+      <c r="P164" s="105">
         <v>120</v>
       </c>
-      <c r="Q164" s="122">
+      <c r="Q164" s="105">
         <v>40</v>
       </c>
       <c r="R164" s="8">
@@ -27802,7 +27802,7 @@
       </c>
       <c r="AP186" s="12"/>
     </row>
-    <row r="187" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="70">
         <v>46191</v>
       </c>
@@ -27821,7 +27821,7 @@
       <c r="F187" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G187" s="126" t="s">
+      <c r="G187" s="109" t="s">
         <v>355</v>
       </c>
       <c r="H187" s="72" t="s">
@@ -27830,27 +27830,27 @@
       <c r="I187" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="J187" s="119"/>
-      <c r="K187" s="122">
-        <v>0</v>
-      </c>
-      <c r="L187" s="122">
-        <v>0</v>
-      </c>
-      <c r="M187" s="122">
+      <c r="J187" s="102"/>
+      <c r="K187" s="105">
+        <v>0</v>
+      </c>
+      <c r="L187" s="105">
+        <v>0</v>
+      </c>
+      <c r="M187" s="105">
         <v>40</v>
       </c>
       <c r="N187" s="8">
         <f t="shared" si="55"/>
         <v>40</v>
       </c>
-      <c r="O187" s="122">
-        <v>0</v>
-      </c>
-      <c r="P187" s="122">
-        <v>0</v>
-      </c>
-      <c r="Q187" s="122">
+      <c r="O187" s="105">
+        <v>0</v>
+      </c>
+      <c r="P187" s="105">
+        <v>0</v>
+      </c>
+      <c r="Q187" s="105">
         <v>40</v>
       </c>
       <c r="R187" s="8">
@@ -27934,7 +27934,7 @@
       </c>
       <c r="AP187" s="12"/>
     </row>
-    <row r="188" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="70">
         <v>46191</v>
       </c>
@@ -27953,7 +27953,7 @@
       <c r="F188" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G188" s="126" t="s">
+      <c r="G188" s="109" t="s">
         <v>355</v>
       </c>
       <c r="H188" s="72" t="s">
@@ -27962,27 +27962,27 @@
       <c r="I188" s="62" t="s">
         <v>309</v>
       </c>
-      <c r="J188" s="119"/>
-      <c r="K188" s="124">
-        <v>40</v>
-      </c>
-      <c r="L188" s="124">
+      <c r="J188" s="102"/>
+      <c r="K188" s="107">
+        <v>40</v>
+      </c>
+      <c r="L188" s="107">
         <v>200</v>
       </c>
-      <c r="M188" s="124">
+      <c r="M188" s="107">
         <v>250</v>
       </c>
       <c r="N188" s="8">
         <f t="shared" si="55"/>
         <v>490</v>
       </c>
-      <c r="O188" s="122">
+      <c r="O188" s="105">
         <v>200</v>
       </c>
-      <c r="P188" s="122">
+      <c r="P188" s="105">
         <v>280</v>
       </c>
-      <c r="Q188" s="122">
+      <c r="Q188" s="105">
         <v>400</v>
       </c>
       <c r="R188" s="8">
@@ -28066,7 +28066,7 @@
       </c>
       <c r="AP188" s="12"/>
     </row>
-    <row r="189" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="70">
         <v>46191</v>
       </c>
@@ -28085,7 +28085,7 @@
       <c r="F189" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G189" s="126" t="s">
+      <c r="G189" s="109" t="s">
         <v>355</v>
       </c>
       <c r="H189" s="72" t="s">
@@ -28094,27 +28094,27 @@
       <c r="I189" s="62" t="s">
         <v>310</v>
       </c>
-      <c r="J189" s="119"/>
-      <c r="K189" s="122">
+      <c r="J189" s="102"/>
+      <c r="K189" s="105">
         <v>120</v>
       </c>
-      <c r="L189" s="122">
+      <c r="L189" s="105">
         <v>240</v>
       </c>
-      <c r="M189" s="122">
+      <c r="M189" s="105">
         <v>100</v>
       </c>
       <c r="N189" s="8">
         <f t="shared" si="55"/>
         <v>460</v>
       </c>
-      <c r="O189" s="122">
+      <c r="O189" s="105">
         <v>166</v>
       </c>
-      <c r="P189" s="122">
+      <c r="P189" s="105">
         <v>280</v>
       </c>
-      <c r="Q189" s="122">
+      <c r="Q189" s="105">
         <v>160</v>
       </c>
       <c r="R189" s="8">
@@ -28198,7 +28198,7 @@
       </c>
       <c r="AP189" s="12"/>
     </row>
-    <row r="190" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="70">
         <v>46191</v>
       </c>
@@ -28217,7 +28217,7 @@
       <c r="F190" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G190" s="126" t="s">
+      <c r="G190" s="109" t="s">
         <v>355</v>
       </c>
       <c r="H190" s="72" t="s">
@@ -28226,27 +28226,27 @@
       <c r="I190" s="62" t="s">
         <v>311</v>
       </c>
-      <c r="J190" s="119"/>
-      <c r="K190" s="122">
+      <c r="J190" s="102"/>
+      <c r="K190" s="105">
         <v>80</v>
       </c>
-      <c r="L190" s="122">
+      <c r="L190" s="105">
         <v>80</v>
       </c>
-      <c r="M190" s="124">
+      <c r="M190" s="107">
         <v>40</v>
       </c>
       <c r="N190" s="8">
         <f t="shared" si="55"/>
         <v>200</v>
       </c>
-      <c r="O190" s="122">
+      <c r="O190" s="105">
         <v>80</v>
       </c>
-      <c r="P190" s="122">
+      <c r="P190" s="105">
         <v>120</v>
       </c>
-      <c r="Q190" s="122">
+      <c r="Q190" s="105">
         <v>80</v>
       </c>
       <c r="R190" s="8">
@@ -28330,7 +28330,7 @@
       </c>
       <c r="AP190" s="12"/>
     </row>
-    <row r="191" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="70">
         <v>46191</v>
       </c>
@@ -28349,7 +28349,7 @@
       <c r="F191" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G191" s="126" t="s">
+      <c r="G191" s="109" t="s">
         <v>355</v>
       </c>
       <c r="H191" s="72" t="s">
@@ -28358,27 +28358,27 @@
       <c r="I191" s="62" t="s">
         <v>312</v>
       </c>
-      <c r="J191" s="119"/>
-      <c r="K191" s="124">
-        <v>40</v>
-      </c>
-      <c r="L191" s="124">
+      <c r="J191" s="102"/>
+      <c r="K191" s="107">
+        <v>40</v>
+      </c>
+      <c r="L191" s="107">
         <v>80</v>
       </c>
-      <c r="M191" s="124">
+      <c r="M191" s="107">
         <v>120</v>
       </c>
       <c r="N191" s="8">
         <f t="shared" si="55"/>
         <v>240</v>
       </c>
-      <c r="O191" s="122">
+      <c r="O191" s="105">
         <v>80</v>
       </c>
-      <c r="P191" s="122">
+      <c r="P191" s="105">
         <v>80</v>
       </c>
-      <c r="Q191" s="122">
+      <c r="Q191" s="105">
         <v>80</v>
       </c>
       <c r="R191" s="8">
@@ -30329,7 +30329,7 @@
       <c r="F206" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G206" s="126" t="s">
+      <c r="G206" s="109" t="s">
         <v>326</v>
       </c>
       <c r="H206" s="72" t="s">
@@ -30338,27 +30338,27 @@
       <c r="I206" s="62" t="s">
         <v>216</v>
       </c>
-      <c r="J206" s="119"/>
-      <c r="K206" s="122">
+      <c r="J206" s="102"/>
+      <c r="K206" s="105">
         <v>800</v>
       </c>
-      <c r="L206" s="122">
+      <c r="L206" s="105">
         <v>1200</v>
       </c>
-      <c r="M206" s="122">
+      <c r="M206" s="105">
         <v>2800</v>
       </c>
       <c r="N206" s="8">
         <f t="shared" si="72"/>
         <v>4800</v>
       </c>
-      <c r="O206" s="122">
+      <c r="O206" s="105">
         <v>1800</v>
       </c>
-      <c r="P206" s="122">
+      <c r="P206" s="105">
         <v>1200</v>
       </c>
-      <c r="Q206" s="122">
+      <c r="Q206" s="105">
         <v>3600</v>
       </c>
       <c r="R206" s="8">
@@ -33084,7 +33084,7 @@
       </c>
       <c r="AP226" s="12"/>
     </row>
-    <row r="227" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="70">
         <v>46192</v>
       </c>
@@ -33103,7 +33103,7 @@
       <c r="F227" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G227" s="126" t="s">
+      <c r="G227" s="109" t="s">
         <v>350</v>
       </c>
       <c r="H227" s="72" t="s">
@@ -33112,27 +33112,27 @@
       <c r="I227" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="J227" s="119"/>
-      <c r="K227" s="124">
+      <c r="J227" s="102"/>
+      <c r="K227" s="107">
         <v>80</v>
       </c>
-      <c r="L227" s="124">
-        <v>0</v>
-      </c>
-      <c r="M227" s="124">
+      <c r="L227" s="107">
+        <v>0</v>
+      </c>
+      <c r="M227" s="107">
         <v>50</v>
       </c>
       <c r="N227" s="8">
         <f t="shared" si="72"/>
         <v>130</v>
       </c>
-      <c r="O227" s="122">
+      <c r="O227" s="105">
         <v>120</v>
       </c>
-      <c r="P227" s="122">
-        <v>0</v>
-      </c>
-      <c r="Q227" s="122">
+      <c r="P227" s="105">
+        <v>0</v>
+      </c>
+      <c r="Q227" s="105">
         <v>400</v>
       </c>
       <c r="R227" s="8">
@@ -33216,7 +33216,7 @@
       </c>
       <c r="AP227" s="12"/>
     </row>
-    <row r="228" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="70">
         <v>46192</v>
       </c>
@@ -33235,7 +33235,7 @@
       <c r="F228" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G228" s="126" t="s">
+      <c r="G228" s="109" t="s">
         <v>351</v>
       </c>
       <c r="H228" s="72" t="s">
@@ -33244,27 +33244,27 @@
       <c r="I228" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="J228" s="119"/>
-      <c r="K228" s="124">
+      <c r="J228" s="102"/>
+      <c r="K228" s="107">
         <v>80</v>
       </c>
-      <c r="L228" s="124">
+      <c r="L228" s="107">
         <v>80</v>
       </c>
-      <c r="M228" s="124">
+      <c r="M228" s="107">
         <v>50</v>
       </c>
       <c r="N228" s="8">
         <f t="shared" si="72"/>
         <v>210</v>
       </c>
-      <c r="O228" s="124">
+      <c r="O228" s="107">
         <v>120</v>
       </c>
-      <c r="P228" s="122">
+      <c r="P228" s="105">
         <v>120</v>
       </c>
-      <c r="Q228" s="124">
+      <c r="Q228" s="107">
         <v>200</v>
       </c>
       <c r="R228" s="8">
@@ -36162,7 +36162,7 @@
       </c>
       <c r="AP249" s="12"/>
     </row>
-    <row r="250" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="70">
         <v>46193</v>
       </c>
@@ -36181,7 +36181,7 @@
       <c r="F250" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G250" s="127" t="s">
+      <c r="G250" s="110" t="s">
         <v>387</v>
       </c>
       <c r="H250" s="100" t="s">
@@ -36190,27 +36190,27 @@
       <c r="I250" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="J250" s="119"/>
-      <c r="K250" s="122">
+      <c r="J250" s="102"/>
+      <c r="K250" s="105">
         <v>314</v>
       </c>
-      <c r="L250" s="122">
+      <c r="L250" s="105">
         <v>353</v>
       </c>
-      <c r="M250" s="122">
+      <c r="M250" s="105">
         <v>388</v>
       </c>
       <c r="N250" s="8">
         <f t="shared" si="72"/>
         <v>1055</v>
       </c>
-      <c r="O250" s="122">
+      <c r="O250" s="105">
         <v>350</v>
       </c>
-      <c r="P250" s="122">
+      <c r="P250" s="105">
         <v>311</v>
       </c>
-      <c r="Q250" s="122">
+      <c r="Q250" s="105">
         <v>396</v>
       </c>
       <c r="R250" s="8">
@@ -36294,7 +36294,7 @@
       </c>
       <c r="AP250" s="12"/>
     </row>
-    <row r="251" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="70">
         <v>46193</v>
       </c>
@@ -36313,7 +36313,7 @@
       <c r="F251" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G251" s="127" t="s">
+      <c r="G251" s="110" t="s">
         <v>388</v>
       </c>
       <c r="H251" s="100" t="s">
@@ -36322,29 +36322,29 @@
       <c r="I251" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="J251" s="119">
-        <v>40</v>
-      </c>
-      <c r="K251" s="122">
-        <v>40</v>
-      </c>
-      <c r="L251" s="122">
-        <v>0</v>
-      </c>
-      <c r="M251" s="122">
+      <c r="J251" s="102">
+        <v>40</v>
+      </c>
+      <c r="K251" s="105">
+        <v>40</v>
+      </c>
+      <c r="L251" s="105">
+        <v>0</v>
+      </c>
+      <c r="M251" s="105">
         <v>120</v>
       </c>
       <c r="N251" s="8">
         <f t="shared" si="72"/>
         <v>160</v>
       </c>
-      <c r="O251" s="122">
+      <c r="O251" s="105">
         <v>200</v>
       </c>
-      <c r="P251" s="122">
-        <v>0</v>
-      </c>
-      <c r="Q251" s="122">
+      <c r="P251" s="105">
+        <v>0</v>
+      </c>
+      <c r="Q251" s="105">
         <v>200</v>
       </c>
       <c r="R251" s="8">
@@ -36682,7 +36682,7 @@
       </c>
       <c r="AP253" s="12"/>
     </row>
-    <row r="254" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="70">
         <v>46195</v>
       </c>
@@ -36701,7 +36701,7 @@
       <c r="F254" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G254" s="127" t="s">
+      <c r="G254" s="110" t="s">
         <v>141</v>
       </c>
       <c r="H254" s="100" t="s">
@@ -36710,27 +36710,27 @@
       <c r="I254" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="J254" s="119"/>
-      <c r="K254" s="122">
+      <c r="J254" s="102"/>
+      <c r="K254" s="105">
         <v>120</v>
       </c>
-      <c r="L254" s="122">
+      <c r="L254" s="105">
         <v>120</v>
       </c>
-      <c r="M254" s="122">
+      <c r="M254" s="105">
         <v>50</v>
       </c>
       <c r="N254" s="8">
         <f t="shared" si="72"/>
         <v>290</v>
       </c>
-      <c r="O254" s="122">
+      <c r="O254" s="105">
         <v>120</v>
       </c>
-      <c r="P254" s="122">
+      <c r="P254" s="105">
         <v>80</v>
       </c>
-      <c r="Q254" s="122">
+      <c r="Q254" s="105">
         <v>80</v>
       </c>
       <c r="R254" s="8">
@@ -46200,7 +46200,7 @@
       </c>
       <c r="AP328" s="12"/>
     </row>
-    <row r="329" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="70">
         <v>46196</v>
       </c>
@@ -46219,7 +46219,7 @@
       <c r="F329" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G329" s="127" t="s">
+      <c r="G329" s="110" t="s">
         <v>355</v>
       </c>
       <c r="H329" s="19" t="s">
@@ -46228,25 +46228,25 @@
       <c r="I329" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="J329" s="119"/>
-      <c r="K329" s="122">
+      <c r="J329" s="102"/>
+      <c r="K329" s="105">
         <v>84</v>
       </c>
-      <c r="L329" s="122">
+      <c r="L329" s="105">
         <v>84</v>
       </c>
-      <c r="M329" s="122"/>
+      <c r="M329" s="105"/>
       <c r="N329" s="8">
         <f t="shared" si="109"/>
         <v>168</v>
       </c>
-      <c r="O329" s="124">
+      <c r="O329" s="107">
         <v>168</v>
       </c>
-      <c r="P329" s="124">
+      <c r="P329" s="107">
         <v>126</v>
       </c>
-      <c r="Q329" s="124">
+      <c r="Q329" s="107">
         <v>252</v>
       </c>
       <c r="R329" s="8">
@@ -46330,7 +46330,7 @@
       </c>
       <c r="AP329" s="12"/>
     </row>
-    <row r="330" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="70">
         <v>46197</v>
       </c>
@@ -46349,7 +46349,7 @@
       <c r="F330" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G330" s="127" t="s">
+      <c r="G330" s="110" t="s">
         <v>477</v>
       </c>
       <c r="H330" s="19" t="s">
@@ -46358,27 +46358,27 @@
       <c r="I330" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="J330" s="119">
+      <c r="J330" s="102">
         <v>80</v>
       </c>
-      <c r="K330" s="122">
+      <c r="K330" s="105">
         <v>80</v>
       </c>
-      <c r="L330" s="122">
+      <c r="L330" s="105">
         <v>80</v>
       </c>
-      <c r="M330" s="122"/>
+      <c r="M330" s="105"/>
       <c r="N330" s="8">
         <f t="shared" si="109"/>
         <v>160</v>
       </c>
-      <c r="O330" s="124">
+      <c r="O330" s="107">
         <v>80</v>
       </c>
-      <c r="P330" s="124">
+      <c r="P330" s="107">
         <v>80</v>
       </c>
-      <c r="Q330" s="124">
+      <c r="Q330" s="107">
         <v>80</v>
       </c>
       <c r="R330" s="8">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="AP332" s="12"/>
     </row>
-    <row r="333" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="70">
         <v>46197</v>
       </c>
@@ -46741,7 +46741,7 @@
       <c r="F333" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G333" s="127" t="s">
+      <c r="G333" s="110" t="s">
         <v>480</v>
       </c>
       <c r="H333" s="19" t="s">
@@ -46751,20 +46751,20 @@
         <v>485</v>
       </c>
       <c r="J333" s="55"/>
-      <c r="K333" s="122"/>
-      <c r="L333" s="122"/>
-      <c r="M333" s="122"/>
+      <c r="K333" s="105"/>
+      <c r="L333" s="105"/>
+      <c r="M333" s="105"/>
       <c r="N333" s="8">
         <f t="shared" si="109"/>
         <v>0</v>
       </c>
-      <c r="O333" s="122">
-        <v>40</v>
-      </c>
-      <c r="P333" s="122">
-        <v>40</v>
-      </c>
-      <c r="Q333" s="122">
+      <c r="O333" s="105">
+        <v>40</v>
+      </c>
+      <c r="P333" s="105">
+        <v>40</v>
+      </c>
+      <c r="Q333" s="105">
         <v>40</v>
       </c>
       <c r="R333" s="8">
@@ -46848,7 +46848,7 @@
       </c>
       <c r="AP333" s="12"/>
     </row>
-    <row r="334" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="70">
         <v>46197</v>
       </c>
@@ -46867,7 +46867,7 @@
       <c r="F334" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G334" s="127" t="s">
+      <c r="G334" s="110" t="s">
         <v>481</v>
       </c>
       <c r="H334" s="19" t="s">
@@ -46877,24 +46877,24 @@
         <v>486</v>
       </c>
       <c r="J334" s="55"/>
-      <c r="K334" s="122">
+      <c r="K334" s="105">
         <v>80</v>
       </c>
-      <c r="L334" s="122">
+      <c r="L334" s="105">
         <v>80</v>
       </c>
-      <c r="M334" s="122"/>
+      <c r="M334" s="105"/>
       <c r="N334" s="8">
         <f t="shared" si="109"/>
         <v>160</v>
       </c>
-      <c r="O334" s="122">
+      <c r="O334" s="105">
         <v>80</v>
       </c>
-      <c r="P334" s="122">
+      <c r="P334" s="105">
         <v>80</v>
       </c>
-      <c r="Q334" s="122">
+      <c r="Q334" s="105">
         <v>80</v>
       </c>
       <c r="R334" s="8">
@@ -46978,7 +46978,7 @@
       </c>
       <c r="AP334" s="12"/>
     </row>
-    <row r="335" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="70">
         <v>46197</v>
       </c>
@@ -46997,7 +46997,7 @@
       <c r="F335" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G335" s="127" t="s">
+      <c r="G335" s="110" t="s">
         <v>482</v>
       </c>
       <c r="H335" s="19" t="s">
@@ -47007,24 +47007,24 @@
         <v>487</v>
       </c>
       <c r="J335" s="55"/>
-      <c r="K335" s="124">
+      <c r="K335" s="107">
         <v>80</v>
       </c>
-      <c r="L335" s="124">
+      <c r="L335" s="107">
         <v>80</v>
       </c>
-      <c r="M335" s="124"/>
+      <c r="M335" s="107"/>
       <c r="N335" s="8">
         <f t="shared" si="109"/>
         <v>160</v>
       </c>
-      <c r="O335" s="122">
+      <c r="O335" s="105">
         <v>80</v>
       </c>
-      <c r="P335" s="122">
+      <c r="P335" s="105">
         <v>120</v>
       </c>
-      <c r="Q335" s="122">
+      <c r="Q335" s="105">
         <v>80</v>
       </c>
       <c r="R335" s="8">
@@ -50464,7 +50464,7 @@
       </c>
       <c r="AP361" s="12"/>
     </row>
-    <row r="362" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="70">
         <v>46202</v>
       </c>
@@ -50483,7 +50483,7 @@
       <c r="F362" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G362" s="127" t="s">
+      <c r="G362" s="110" t="s">
         <v>220</v>
       </c>
       <c r="H362" s="19" t="s">
@@ -50493,24 +50493,24 @@
         <v>223</v>
       </c>
       <c r="J362" s="55"/>
-      <c r="K362" s="124">
+      <c r="K362" s="107">
         <v>160</v>
       </c>
-      <c r="L362" s="124">
+      <c r="L362" s="107">
         <v>280</v>
       </c>
-      <c r="M362" s="124"/>
+      <c r="M362" s="107"/>
       <c r="N362" s="8">
         <f t="shared" si="109"/>
         <v>440</v>
       </c>
-      <c r="O362" s="122">
+      <c r="O362" s="105">
         <v>280</v>
       </c>
-      <c r="P362" s="124">
+      <c r="P362" s="107">
         <v>280</v>
       </c>
-      <c r="Q362" s="124">
+      <c r="Q362" s="107">
         <v>520</v>
       </c>
       <c r="R362" s="8">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="AP362" s="12"/>
     </row>
-    <row r="363" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="70">
         <v>46202</v>
       </c>
@@ -50613,7 +50613,7 @@
       <c r="F363" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G363" s="127" t="s">
+      <c r="G363" s="110" t="s">
         <v>516</v>
       </c>
       <c r="H363" s="19" t="s">
@@ -50623,20 +50623,20 @@
         <v>485</v>
       </c>
       <c r="J363" s="55"/>
-      <c r="K363" s="122"/>
-      <c r="L363" s="122"/>
-      <c r="M363" s="124"/>
+      <c r="K363" s="105"/>
+      <c r="L363" s="105"/>
+      <c r="M363" s="107"/>
       <c r="N363" s="8">
         <f t="shared" si="109"/>
         <v>0</v>
       </c>
-      <c r="O363" s="124">
-        <v>40</v>
-      </c>
-      <c r="P363" s="124">
-        <v>40</v>
-      </c>
-      <c r="Q363" s="124">
+      <c r="O363" s="107">
+        <v>40</v>
+      </c>
+      <c r="P363" s="107">
+        <v>40</v>
+      </c>
+      <c r="Q363" s="107">
         <v>120</v>
       </c>
       <c r="R363" s="8">
@@ -50720,7 +50720,7 @@
       </c>
       <c r="AP363" s="12"/>
     </row>
-    <row r="364" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="70">
         <v>46202</v>
       </c>
@@ -50739,7 +50739,7 @@
       <c r="F364" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G364" s="127" t="s">
+      <c r="G364" s="110" t="s">
         <v>517</v>
       </c>
       <c r="H364" s="19" t="s">
@@ -50749,24 +50749,24 @@
         <v>518</v>
       </c>
       <c r="J364" s="55"/>
-      <c r="K364" s="124">
+      <c r="K364" s="107">
         <v>80</v>
       </c>
-      <c r="L364" s="124">
-        <v>40</v>
-      </c>
-      <c r="M364" s="124"/>
+      <c r="L364" s="107">
+        <v>40</v>
+      </c>
+      <c r="M364" s="107"/>
       <c r="N364" s="8">
         <f t="shared" si="109"/>
         <v>120</v>
       </c>
-      <c r="O364" s="122">
+      <c r="O364" s="105">
         <v>80</v>
       </c>
-      <c r="P364" s="122">
-        <v>40</v>
-      </c>
-      <c r="Q364" s="124">
+      <c r="P364" s="105">
+        <v>40</v>
+      </c>
+      <c r="Q364" s="107">
         <v>80</v>
       </c>
       <c r="R364" s="8">
@@ -58189,37 +58189,8 @@
     </filterColumn>
     <filterColumn colId="6">
       <filters>
-        <filter val="24/7 Mart"/>
-        <filter val="4 Reason"/>
         <filter val="Al Fatah"/>
-        <filter val="Al Raheem Iqbal Town"/>
-        <filter val="Al Raheem Wapda Town"/>
         <filter val="Al-Fatah"/>
-        <filter val="Asgher Store"/>
-        <filter val="Aslam Super Mart"/>
-        <filter val="Clinix"/>
-        <filter val="Crown"/>
-        <filter val="Euro Store"/>
-        <filter val="Galaxy Super Market"/>
-        <filter val="Jalal Sons"/>
-        <filter val="Jalal sons Askari 10"/>
-        <filter val="Jalal Sons Bahria Orchard"/>
-        <filter val="Jalal Sons Behria Orchard"/>
-        <filter val="Jalal Sons Lake City"/>
-        <filter val="Jalal sons main market"/>
-        <filter val="Jalal Sons phase 5"/>
-        <filter val="Lake City Mart"/>
-        <filter val="MB Traders"/>
-        <filter val="Ms Traders (Risen)"/>
-        <filter val="Pak Madina (Jharawala)"/>
-        <filter val="Rafaqat &amp; Sons"/>
-        <filter val="Rainbow BT"/>
-        <filter val="Rainbow Cash &amp; Carry"/>
-        <filter val="Rehman Garden (Risen)"/>
-        <filter val="Risan Askari 11"/>
-        <filter val="Sana Cash &amp; Carry"/>
-        <filter val="Shehwar Mega Mart"/>
-        <filter val="Swera Store"/>
       </filters>
     </filterColumn>
     <filterColumn colId="10" showButton="0"/>
@@ -58236,13 +58207,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -58255,14 +58227,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58288,22 +58259,22 @@
   <sheetData>
     <row r="3" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="4:8" ht="22.5" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="115"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="124"/>
     </row>
     <row r="5" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D5" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
     </row>
     <row r="6" spans="4:8" x14ac:dyDescent="0.35">
       <c r="D6" s="23" t="s">
@@ -58866,10 +58837,10 @@
       </c>
     </row>
     <row r="31" spans="3:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C31" s="117" t="s">
+      <c r="C31" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="118"/>
+      <c r="D31" s="127"/>
       <c r="E31" s="50">
         <f>SUM(E24:E30)</f>
         <v>8000</v>
